--- a/research/traditional_assets/database/data/philippines/philippines_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/philippines/philippines_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.08470478478571676</v>
+        <v>0.08452677282375247</v>
       </c>
       <c r="C2">
-        <v>410.8838238816762</v>
+        <v>407.7216692473249</v>
       </c>
       <c r="D2">
-        <v>337.3838238816762</v>
+        <v>338.3146692473249</v>
       </c>
       <c r="E2">
-        <v>-63.49999999999999</v>
+        <v>-59.407</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>4.093</v>
       </c>
       <c r="G2">
         <v>73.5</v>
@@ -1451,28 +1451,28 @@
         <v>62.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2058779</v>
       </c>
       <c r="N2">
-        <v>62.4</v>
+        <v>62.1941221</v>
       </c>
       <c r="O2">
-        <v>15.6</v>
+        <v>15.548530525</v>
       </c>
       <c r="P2">
-        <v>46.8</v>
+        <v>46.645591575</v>
       </c>
       <c r="Q2">
-        <v>63.2</v>
+        <v>63.045591575</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.08470478478571676</v>
+        <v>0.08499951800379038</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706918</v>
+        <v>0.5704007501151668</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>303.0922697385198</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08452677282375247</v>
+        <v>0.08434876086178821</v>
       </c>
       <c r="C3">
-        <v>407.7216692473249</v>
+        <v>404.5646652470892</v>
       </c>
       <c r="D3">
-        <v>338.3146692473249</v>
+        <v>339.2506652470892</v>
       </c>
       <c r="E3">
-        <v>-59.407</v>
+        <v>-55.31399999999999</v>
       </c>
       <c r="F3">
-        <v>4.093</v>
+        <v>8.186</v>
       </c>
       <c r="G3">
         <v>73.5</v>
@@ -1533,28 +1533,28 @@
         <v>62.4</v>
       </c>
       <c r="M3">
-        <v>0.2058779</v>
+        <v>0.4117557999999999</v>
       </c>
       <c r="N3">
-        <v>62.1941221</v>
+        <v>61.9882442</v>
       </c>
       <c r="O3">
-        <v>15.548530525</v>
+        <v>15.49706105</v>
       </c>
       <c r="P3">
-        <v>46.645591575</v>
+        <v>46.49118315</v>
       </c>
       <c r="Q3">
-        <v>63.045591575</v>
+        <v>62.89118315</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08499951800379038</v>
+        <v>0.08530026618549816</v>
       </c>
       <c r="T3">
-        <v>0.5704007501151668</v>
+        <v>0.574777002609529</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>303.0922697385198</v>
+        <v>151.5461348692599</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08434876086178821</v>
+        <v>0.08417074889982389</v>
       </c>
       <c r="C4">
-        <v>404.5646652470892</v>
+        <v>401.4128547494731</v>
       </c>
       <c r="D4">
-        <v>339.2506652470892</v>
+        <v>340.1918547494731</v>
       </c>
       <c r="E4">
-        <v>-55.31399999999999</v>
+        <v>-51.22099999999999</v>
       </c>
       <c r="F4">
-        <v>8.186</v>
+        <v>12.279</v>
       </c>
       <c r="G4">
         <v>73.5</v>
@@ -1615,28 +1615,28 @@
         <v>62.4</v>
       </c>
       <c r="M4">
-        <v>0.4117557999999999</v>
+        <v>0.6176337</v>
       </c>
       <c r="N4">
-        <v>61.9882442</v>
+        <v>61.7823663</v>
       </c>
       <c r="O4">
-        <v>15.49706105</v>
+        <v>15.445591575</v>
       </c>
       <c r="P4">
-        <v>46.49118315</v>
+        <v>46.336774725</v>
       </c>
       <c r="Q4">
-        <v>62.89118315</v>
+        <v>62.736774725</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08530026618549816</v>
+        <v>0.08560721536064318</v>
       </c>
       <c r="T4">
-        <v>0.574777002609529</v>
+        <v>0.5792434871140841</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>151.5461348692599</v>
+        <v>101.0307565795066</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08417074889982389</v>
+        <v>0.08399273693785958</v>
       </c>
       <c r="C5">
-        <v>401.4128547494731</v>
+        <v>398.2662811000263</v>
       </c>
       <c r="D5">
-        <v>340.1918547494731</v>
+        <v>341.1382811000263</v>
       </c>
       <c r="E5">
-        <v>-51.22099999999999</v>
+        <v>-47.12799999999999</v>
       </c>
       <c r="F5">
-        <v>12.279</v>
+        <v>16.372</v>
       </c>
       <c r="G5">
         <v>73.5</v>
@@ -1697,28 +1697,28 @@
         <v>62.4</v>
       </c>
       <c r="M5">
-        <v>0.6176337</v>
+        <v>0.8235115999999999</v>
       </c>
       <c r="N5">
-        <v>61.7823663</v>
+        <v>61.5764884</v>
       </c>
       <c r="O5">
-        <v>15.445591575</v>
+        <v>15.3941221</v>
       </c>
       <c r="P5">
-        <v>46.336774725</v>
+        <v>46.1823663</v>
       </c>
       <c r="Q5">
-        <v>62.736774725</v>
+        <v>62.5823663</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08560721536064318</v>
+        <v>0.0859205593102704</v>
       </c>
       <c r="T5">
-        <v>0.5792434871140841</v>
+        <v>0.5838030233791509</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>101.0307565795066</v>
+        <v>75.77306743462995</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08399273693785958</v>
+        <v>0.0838147249758953</v>
       </c>
       <c r="C6">
-        <v>398.2662811000263</v>
+        <v>395.1249881280007</v>
       </c>
       <c r="D6">
-        <v>341.1382811000263</v>
+        <v>342.0899881280008</v>
       </c>
       <c r="E6">
-        <v>-47.12799999999999</v>
+        <v>-43.03499999999999</v>
       </c>
       <c r="F6">
-        <v>16.372</v>
+        <v>20.465</v>
       </c>
       <c r="G6">
         <v>73.5</v>
@@ -1779,28 +1779,28 @@
         <v>62.4</v>
       </c>
       <c r="M6">
-        <v>0.8235115999999999</v>
+        <v>1.0293895</v>
       </c>
       <c r="N6">
-        <v>61.5764884</v>
+        <v>61.3706105</v>
       </c>
       <c r="O6">
-        <v>15.3941221</v>
+        <v>15.342652625</v>
       </c>
       <c r="P6">
-        <v>46.1823663</v>
+        <v>46.027957875</v>
       </c>
       <c r="Q6">
-        <v>62.5823663</v>
+        <v>62.427957875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.0859205593102704</v>
+        <v>0.08624049997462663</v>
       </c>
       <c r="T6">
-        <v>0.5838030233791509</v>
+        <v>0.588458549881377</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>75.77306743462995</v>
+        <v>60.61845394770394</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0838147249758953</v>
+        <v>0.08363671301393101</v>
       </c>
       <c r="C7">
-        <v>395.1249881280007</v>
+        <v>391.9890201531159</v>
       </c>
       <c r="D7">
-        <v>342.0899881280008</v>
+        <v>343.0470201531159</v>
       </c>
       <c r="E7">
-        <v>-43.03499999999999</v>
+        <v>-38.94199999999999</v>
       </c>
       <c r="F7">
-        <v>20.465</v>
+        <v>24.558</v>
       </c>
       <c r="G7">
         <v>73.5</v>
@@ -1861,28 +1861,28 @@
         <v>62.4</v>
       </c>
       <c r="M7">
-        <v>1.0293895</v>
+        <v>1.2352674</v>
       </c>
       <c r="N7">
-        <v>61.3706105</v>
+        <v>61.1647326</v>
       </c>
       <c r="O7">
-        <v>15.342652625</v>
+        <v>15.29118315</v>
       </c>
       <c r="P7">
-        <v>46.027957875</v>
+        <v>45.87354945</v>
       </c>
       <c r="Q7">
-        <v>62.427957875</v>
+        <v>62.27354945</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08624049997462663</v>
+        <v>0.08656724788716065</v>
       </c>
       <c r="T7">
-        <v>0.588458549881377</v>
+        <v>0.5932131301389696</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>60.61845394770394</v>
+        <v>50.51537828975329</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08363671301393101</v>
+        <v>0.08345870105196672</v>
       </c>
       <c r="C8">
-        <v>391.9890201531159</v>
+        <v>388.8584219924381</v>
       </c>
       <c r="D8">
-        <v>343.0470201531159</v>
+        <v>344.0094219924381</v>
       </c>
       <c r="E8">
-        <v>-38.94199999999999</v>
+        <v>-34.849</v>
       </c>
       <c r="F8">
-        <v>24.558</v>
+        <v>28.651</v>
       </c>
       <c r="G8">
         <v>73.5</v>
@@ -1943,28 +1943,28 @@
         <v>62.4</v>
       </c>
       <c r="M8">
-        <v>1.2352674</v>
+        <v>1.4411453</v>
       </c>
       <c r="N8">
-        <v>61.1647326</v>
+        <v>60.9588547</v>
       </c>
       <c r="O8">
-        <v>15.29118315</v>
+        <v>15.239713675</v>
       </c>
       <c r="P8">
-        <v>45.87354945</v>
+        <v>45.719141025</v>
       </c>
       <c r="Q8">
-        <v>62.27354945</v>
+        <v>62.119141025</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08656724788716065</v>
+        <v>0.08690102263652336</v>
       </c>
       <c r="T8">
-        <v>0.5932131301389696</v>
+        <v>0.5980699594343599</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>50.5153782897533</v>
+        <v>43.2988956769314</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08345870105196672</v>
+        <v>0.08328068909000244</v>
       </c>
       <c r="C9">
-        <v>388.8584219924381</v>
+        <v>385.7332389673772</v>
       </c>
       <c r="D9">
-        <v>344.0094219924381</v>
+        <v>344.9772389673773</v>
       </c>
       <c r="E9">
-        <v>-34.84899999999999</v>
+        <v>-30.75599999999999</v>
       </c>
       <c r="F9">
-        <v>28.651</v>
+        <v>32.744</v>
       </c>
       <c r="G9">
         <v>73.5</v>
@@ -2025,28 +2025,28 @@
         <v>62.4</v>
       </c>
       <c r="M9">
-        <v>1.4411453</v>
+        <v>1.6470232</v>
       </c>
       <c r="N9">
-        <v>60.9588547</v>
+        <v>60.7529768</v>
       </c>
       <c r="O9">
-        <v>15.239713675</v>
+        <v>15.1882442</v>
       </c>
       <c r="P9">
-        <v>45.719141025</v>
+        <v>45.5647326</v>
       </c>
       <c r="Q9">
-        <v>62.119141025</v>
+        <v>61.9647326</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08690102263652336</v>
+        <v>0.08724205335869831</v>
       </c>
       <c r="T9">
-        <v>0.5980699594343599</v>
+        <v>0.6030323719753022</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>43.29889567693139</v>
+        <v>37.88653371731498</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08328068909000244</v>
+        <v>0.08310267712803814</v>
       </c>
       <c r="C10">
-        <v>385.7332389673772</v>
+        <v>382.6135169108013</v>
       </c>
       <c r="D10">
-        <v>344.9772389673773</v>
+        <v>345.9505169108013</v>
       </c>
       <c r="E10">
-        <v>-30.75599999999999</v>
+        <v>-26.663</v>
       </c>
       <c r="F10">
-        <v>32.744</v>
+        <v>36.837</v>
       </c>
       <c r="G10">
         <v>73.5</v>
@@ -2107,28 +2107,28 @@
         <v>62.4</v>
       </c>
       <c r="M10">
-        <v>1.6470232</v>
+        <v>1.8529011</v>
       </c>
       <c r="N10">
-        <v>60.7529768</v>
+        <v>60.5470989</v>
       </c>
       <c r="O10">
-        <v>15.1882442</v>
+        <v>15.136774725</v>
       </c>
       <c r="P10">
-        <v>45.5647326</v>
+        <v>45.410324175</v>
       </c>
       <c r="Q10">
-        <v>61.9647326</v>
+        <v>61.810324175</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08724205335869831</v>
+        <v>0.08759057926158037</v>
       </c>
       <c r="T10">
-        <v>0.6030323719753022</v>
+        <v>0.6081038485281333</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>37.88653371731498</v>
+        <v>33.67691885983554</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08310267712803814</v>
+        <v>0.08292466516607384</v>
       </c>
       <c r="C11">
-        <v>382.6135169108013</v>
+        <v>379.4993021742708</v>
       </c>
       <c r="D11">
-        <v>345.9505169108013</v>
+        <v>346.9293021742708</v>
       </c>
       <c r="E11">
-        <v>-26.663</v>
+        <v>-22.56999999999999</v>
       </c>
       <c r="F11">
-        <v>36.837</v>
+        <v>40.93</v>
       </c>
       <c r="G11">
         <v>73.5</v>
@@ -2189,28 +2189,28 @@
         <v>62.4</v>
       </c>
       <c r="M11">
-        <v>1.8529011</v>
+        <v>2.058779</v>
       </c>
       <c r="N11">
-        <v>60.5470989</v>
+        <v>60.341221</v>
       </c>
       <c r="O11">
-        <v>15.136774725</v>
+        <v>15.08530525</v>
       </c>
       <c r="P11">
-        <v>45.410324175</v>
+        <v>45.25591575</v>
       </c>
       <c r="Q11">
-        <v>61.810324175</v>
+        <v>61.65591575</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08759057926158037</v>
+        <v>0.0879468501845265</v>
       </c>
       <c r="T11">
-        <v>0.6081038485281333</v>
+        <v>0.6132880245599162</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>33.67691885983554</v>
+        <v>30.30922697385198</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08292466516607384</v>
+        <v>0.08274665320410957</v>
       </c>
       <c r="C12">
-        <v>379.4993021742708</v>
+        <v>376.3906416353983</v>
       </c>
       <c r="D12">
-        <v>346.9293021742708</v>
+        <v>347.9136416353983</v>
       </c>
       <c r="E12">
-        <v>-22.56999999999999</v>
+        <v>-18.47699999999999</v>
       </c>
       <c r="F12">
-        <v>40.93000000000001</v>
+        <v>45.023</v>
       </c>
       <c r="G12">
         <v>73.5</v>
@@ -2271,28 +2271,28 @@
         <v>62.4</v>
       </c>
       <c r="M12">
-        <v>2.058779</v>
+        <v>2.2646569</v>
       </c>
       <c r="N12">
-        <v>60.341221</v>
+        <v>60.1353431</v>
       </c>
       <c r="O12">
-        <v>15.08530525</v>
+        <v>15.033835775</v>
       </c>
       <c r="P12">
-        <v>45.25591575</v>
+        <v>45.101507325</v>
       </c>
       <c r="Q12">
-        <v>61.65591575</v>
+        <v>61.501507325</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.0879468501845265</v>
+        <v>0.08831112719562872</v>
       </c>
       <c r="T12">
-        <v>0.6132880245599162</v>
+        <v>0.618588698929492</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>30.30922697385197</v>
+        <v>27.5538427035018</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08274665320410957</v>
+        <v>0.08256864124214527</v>
       </c>
       <c r="C13">
-        <v>376.3906416353983</v>
+        <v>373.2875827053317</v>
       </c>
       <c r="D13">
-        <v>347.9136416353983</v>
+        <v>348.9035827053316</v>
       </c>
       <c r="E13">
-        <v>-18.47699999999999</v>
+        <v>-14.38399999999999</v>
       </c>
       <c r="F13">
-        <v>45.023</v>
+        <v>49.116</v>
       </c>
       <c r="G13">
         <v>73.5</v>
@@ -2353,28 +2353,28 @@
         <v>62.4</v>
       </c>
       <c r="M13">
-        <v>2.2646569</v>
+        <v>2.4705348</v>
       </c>
       <c r="N13">
-        <v>60.1353431</v>
+        <v>59.9294652</v>
       </c>
       <c r="O13">
-        <v>15.033835775</v>
+        <v>14.9823663</v>
       </c>
       <c r="P13">
-        <v>45.101507325</v>
+        <v>44.9470989</v>
       </c>
       <c r="Q13">
-        <v>61.501507325</v>
+        <v>61.3470989</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.08831112719562872</v>
+        <v>0.08868368322971053</v>
       </c>
       <c r="T13">
-        <v>0.618588698929492</v>
+        <v>0.6240098431711035</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>27.5538427035018</v>
+        <v>25.25768914487665</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08256864124214527</v>
+        <v>0.08239062928018095</v>
       </c>
       <c r="C14">
-        <v>373.2875827053317</v>
+        <v>370.1901733363665</v>
       </c>
       <c r="D14">
-        <v>348.9035827053316</v>
+        <v>349.8991733363665</v>
       </c>
       <c r="E14">
-        <v>-14.38399999999999</v>
+        <v>-10.29099999999999</v>
       </c>
       <c r="F14">
-        <v>49.116</v>
+        <v>53.209</v>
       </c>
       <c r="G14">
         <v>73.5</v>
@@ -2435,28 +2435,28 @@
         <v>62.4</v>
       </c>
       <c r="M14">
-        <v>2.4705348</v>
+        <v>2.6764127</v>
       </c>
       <c r="N14">
-        <v>59.9294652</v>
+        <v>59.7235873</v>
       </c>
       <c r="O14">
-        <v>14.9823663</v>
+        <v>14.930896825</v>
       </c>
       <c r="P14">
-        <v>44.9470989</v>
+        <v>44.792690475</v>
       </c>
       <c r="Q14">
-        <v>61.3470989</v>
+        <v>61.192690475</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.08868368322971053</v>
+        <v>0.08906480377032294</v>
       </c>
       <c r="T14">
-        <v>0.6240098431711035</v>
+        <v>0.6295556114182693</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>25.25768914487665</v>
+        <v>23.31478997988613</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08239062928018095</v>
+        <v>0.08221261731821666</v>
       </c>
       <c r="C15">
-        <v>370.1901733363665</v>
+        <v>367.0984620296889</v>
       </c>
       <c r="D15">
-        <v>349.8991733363665</v>
+        <v>350.9004620296889</v>
       </c>
       <c r="E15">
-        <v>-10.29099999999999</v>
+        <v>-6.197999999999986</v>
       </c>
       <c r="F15">
-        <v>53.209</v>
+        <v>57.30200000000001</v>
       </c>
       <c r="G15">
         <v>73.5</v>
@@ -2517,28 +2517,28 @@
         <v>62.4</v>
       </c>
       <c r="M15">
-        <v>2.6764127</v>
+        <v>2.8822906</v>
       </c>
       <c r="N15">
-        <v>59.7235873</v>
+        <v>59.5177094</v>
       </c>
       <c r="O15">
-        <v>14.930896825</v>
+        <v>14.87942735</v>
       </c>
       <c r="P15">
-        <v>44.792690475</v>
+        <v>44.63828205</v>
       </c>
       <c r="Q15">
-        <v>61.192690475</v>
+        <v>61.03828205</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08906480377032294</v>
+        <v>0.08945478757932171</v>
       </c>
       <c r="T15">
-        <v>0.6295556114182693</v>
+        <v>0.6352303510200205</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>23.31478997988613</v>
+        <v>21.6494478384657</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08221261731821666</v>
+        <v>0.08203460535625239</v>
       </c>
       <c r="C16">
-        <v>367.0984620296889</v>
+        <v>364.0124978432519</v>
       </c>
       <c r="D16">
-        <v>350.9004620296889</v>
+        <v>351.9074978432519</v>
       </c>
       <c r="E16">
-        <v>-6.197999999999986</v>
+        <v>-2.104999999999983</v>
       </c>
       <c r="F16">
-        <v>57.30200000000001</v>
+        <v>61.39500000000001</v>
       </c>
       <c r="G16">
         <v>73.5</v>
@@ -2599,28 +2599,28 @@
         <v>62.4</v>
       </c>
       <c r="M16">
-        <v>2.8822906</v>
+        <v>3.088168500000001</v>
       </c>
       <c r="N16">
-        <v>59.5177094</v>
+        <v>59.3118315</v>
       </c>
       <c r="O16">
-        <v>14.87942735</v>
+        <v>14.827957875</v>
       </c>
       <c r="P16">
-        <v>44.63828205</v>
+        <v>44.483873625</v>
       </c>
       <c r="Q16">
-        <v>61.03828205</v>
+        <v>60.883873625</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08945478757932171</v>
+        <v>0.08985394747794398</v>
       </c>
       <c r="T16">
-        <v>0.6352303510200205</v>
+        <v>0.6410386139065186</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.6494478384657</v>
+        <v>20.20615131590131</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08203460535625239</v>
+        <v>0.08185659339428809</v>
       </c>
       <c r="C17">
-        <v>364.0124978432519</v>
+        <v>360.9323303997876</v>
       </c>
       <c r="D17">
-        <v>351.9074978432519</v>
+        <v>352.9203303997876</v>
       </c>
       <c r="E17">
-        <v>-2.104999999999997</v>
+        <v>1.988000000000007</v>
       </c>
       <c r="F17">
-        <v>61.395</v>
+        <v>65.488</v>
       </c>
       <c r="G17">
         <v>73.5</v>
@@ -2681,28 +2681,28 @@
         <v>62.4</v>
       </c>
       <c r="M17">
-        <v>3.0881685</v>
+        <v>3.2940464</v>
       </c>
       <c r="N17">
-        <v>59.3118315</v>
+        <v>59.1059536</v>
       </c>
       <c r="O17">
-        <v>14.827957875</v>
+        <v>14.7764884</v>
       </c>
       <c r="P17">
-        <v>44.483873625</v>
+        <v>44.3294652</v>
       </c>
       <c r="Q17">
-        <v>60.883873625</v>
+        <v>60.7294652</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08985394747794398</v>
+        <v>0.0902626111836763</v>
       </c>
       <c r="T17">
-        <v>0.6410386139065186</v>
+        <v>0.6469851687665049</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>20.20615131590132</v>
+        <v>18.94326685865749</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08185659339428809</v>
+        <v>0.08167858143232379</v>
       </c>
       <c r="C18">
-        <v>360.9323303997876</v>
+        <v>357.8580098949581</v>
       </c>
       <c r="D18">
-        <v>352.9203303997876</v>
+        <v>353.9390098949581</v>
       </c>
       <c r="E18">
-        <v>1.988000000000007</v>
+        <v>6.08100000000001</v>
       </c>
       <c r="F18">
-        <v>65.488</v>
+        <v>69.581</v>
       </c>
       <c r="G18">
         <v>73.5</v>
@@ -2763,28 +2763,28 @@
         <v>62.4</v>
       </c>
       <c r="M18">
-        <v>3.2940464</v>
+        <v>3.4999243</v>
       </c>
       <c r="N18">
-        <v>59.1059536</v>
+        <v>58.9000757</v>
       </c>
       <c r="O18">
-        <v>14.7764884</v>
+        <v>14.725018925</v>
       </c>
       <c r="P18">
-        <v>44.3294652</v>
+        <v>44.175056775</v>
       </c>
       <c r="Q18">
-        <v>60.7294652</v>
+        <v>60.575056775</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.0902626111836763</v>
+        <v>0.09068112220761904</v>
       </c>
       <c r="T18">
-        <v>0.6469851687665049</v>
+        <v>0.6530750141050452</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.94326685865749</v>
+        <v>17.82895704344234</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08167858143232379</v>
+        <v>0.08150056947035951</v>
       </c>
       <c r="C19">
-        <v>357.8580098949581</v>
+        <v>354.7895871056475</v>
       </c>
       <c r="D19">
-        <v>353.9390098949581</v>
+        <v>354.9635871056475</v>
       </c>
       <c r="E19">
-        <v>6.08100000000001</v>
+        <v>10.17400000000001</v>
       </c>
       <c r="F19">
-        <v>69.581</v>
+        <v>73.67400000000001</v>
       </c>
       <c r="G19">
         <v>73.5</v>
@@ -2845,28 +2845,28 @@
         <v>62.4</v>
       </c>
       <c r="M19">
-        <v>3.4999243</v>
+        <v>3.7058022</v>
       </c>
       <c r="N19">
-        <v>58.9000757</v>
+        <v>58.6941978</v>
       </c>
       <c r="O19">
-        <v>14.725018925</v>
+        <v>14.67354945</v>
       </c>
       <c r="P19">
-        <v>44.175056775</v>
+        <v>44.02064835</v>
       </c>
       <c r="Q19">
-        <v>60.575056775</v>
+        <v>60.42064835</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09068112220761904</v>
+        <v>0.0911098408175116</v>
       </c>
       <c r="T19">
-        <v>0.6530750141050452</v>
+        <v>0.6593133922567204</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.82895704344234</v>
+        <v>16.83845942991777</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08150056947035952</v>
+        <v>0.08132255750839522</v>
       </c>
       <c r="C20">
-        <v>354.7895871056475</v>
+        <v>351.7271133984003</v>
       </c>
       <c r="D20">
-        <v>354.9635871056474</v>
+        <v>355.9941133984003</v>
       </c>
       <c r="E20">
-        <v>10.174</v>
+        <v>14.26700000000002</v>
       </c>
       <c r="F20">
-        <v>73.67399999999999</v>
+        <v>77.76700000000001</v>
       </c>
       <c r="G20">
         <v>73.5</v>
@@ -2927,28 +2927,28 @@
         <v>62.4</v>
       </c>
       <c r="M20">
-        <v>3.705802199999999</v>
+        <v>3.9116801</v>
       </c>
       <c r="N20">
-        <v>58.6941978</v>
+        <v>58.4883199</v>
       </c>
       <c r="O20">
-        <v>14.67354945</v>
+        <v>14.622079975</v>
       </c>
       <c r="P20">
-        <v>44.02064835</v>
+        <v>43.866239925</v>
       </c>
       <c r="Q20">
-        <v>60.42064835</v>
+        <v>60.266239925</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0911098408175116</v>
+        <v>0.09154914507209286</v>
       </c>
       <c r="T20">
-        <v>0.6593133922567204</v>
+        <v>0.6657058044368321</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.83845942991777</v>
+        <v>15.95222472307999</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08132255750839522</v>
+        <v>0.08114454554643093</v>
       </c>
       <c r="C21">
-        <v>351.7271133984003</v>
+        <v>348.6706407380041</v>
       </c>
       <c r="D21">
-        <v>355.9941133984003</v>
+        <v>357.0306407380041</v>
       </c>
       <c r="E21">
-        <v>14.26700000000002</v>
+        <v>18.36000000000002</v>
       </c>
       <c r="F21">
-        <v>77.76700000000001</v>
+        <v>81.86000000000001</v>
       </c>
       <c r="G21">
         <v>73.5</v>
@@ -3009,28 +3009,28 @@
         <v>62.4</v>
       </c>
       <c r="M21">
-        <v>3.9116801</v>
+        <v>4.117558000000001</v>
       </c>
       <c r="N21">
-        <v>58.4883199</v>
+        <v>58.282442</v>
       </c>
       <c r="O21">
-        <v>14.622079975</v>
+        <v>14.5706105</v>
       </c>
       <c r="P21">
-        <v>43.866239925</v>
+        <v>43.7118315</v>
       </c>
       <c r="Q21">
-        <v>60.266239925</v>
+        <v>60.11183149999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09154914507209286</v>
+        <v>0.09199943193303867</v>
       </c>
       <c r="T21">
-        <v>0.6657058044368321</v>
+        <v>0.6722580269214465</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.95222472307999</v>
+        <v>15.15461348692599</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08114454554643093</v>
+        <v>0.08096653358446664</v>
       </c>
       <c r="C22">
-        <v>348.6706407380041</v>
+        <v>345.6202216962258</v>
       </c>
       <c r="D22">
-        <v>357.0306407380041</v>
+        <v>358.0732216962259</v>
       </c>
       <c r="E22">
-        <v>18.36000000000002</v>
+        <v>22.45300000000002</v>
       </c>
       <c r="F22">
-        <v>81.86000000000001</v>
+        <v>85.95300000000002</v>
       </c>
       <c r="G22">
         <v>73.5</v>
@@ -3091,28 +3091,28 @@
         <v>62.4</v>
       </c>
       <c r="M22">
-        <v>4.117558000000001</v>
+        <v>4.323435900000001</v>
       </c>
       <c r="N22">
-        <v>58.282442</v>
+        <v>58.0765641</v>
       </c>
       <c r="O22">
-        <v>14.5706105</v>
+        <v>14.519141025</v>
       </c>
       <c r="P22">
-        <v>43.7118315</v>
+        <v>43.557423075</v>
       </c>
       <c r="Q22">
-        <v>60.11183149999999</v>
+        <v>59.957423075</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09199943193303867</v>
+        <v>0.09246111846135016</v>
       </c>
       <c r="T22">
-        <v>0.6722580269214465</v>
+        <v>0.6789761284563044</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>15.15461348692599</v>
+        <v>14.4329652256438</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08096653358446662</v>
+        <v>0.08078852162250234</v>
       </c>
       <c r="C23">
-        <v>345.6202216962259</v>
+        <v>342.5759094606989</v>
       </c>
       <c r="D23">
-        <v>358.0732216962259</v>
+        <v>359.1219094606989</v>
       </c>
       <c r="E23">
-        <v>22.45300000000001</v>
+        <v>26.54600000000001</v>
       </c>
       <c r="F23">
-        <v>85.953</v>
+        <v>90.04600000000001</v>
       </c>
       <c r="G23">
         <v>73.5</v>
@@ -3173,28 +3173,28 @@
         <v>62.4</v>
       </c>
       <c r="M23">
-        <v>4.3234359</v>
+        <v>4.5293138</v>
       </c>
       <c r="N23">
-        <v>58.0765641</v>
+        <v>57.8706862</v>
       </c>
       <c r="O23">
-        <v>14.519141025</v>
+        <v>14.46767155</v>
       </c>
       <c r="P23">
-        <v>43.557423075</v>
+        <v>43.40301465</v>
       </c>
       <c r="Q23">
-        <v>59.957423075</v>
+        <v>59.80301465</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09246111846135016</v>
+        <v>0.09293464310577224</v>
       </c>
       <c r="T23">
-        <v>0.6789761284563044</v>
+        <v>0.6858664890048766</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.4329652256438</v>
+        <v>13.7769213517509</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08078852162250234</v>
+        <v>0.08061050966053805</v>
       </c>
       <c r="C24">
-        <v>342.5759094606989</v>
+        <v>339.537757843969</v>
       </c>
       <c r="D24">
-        <v>359.1219094606989</v>
+        <v>360.176757843969</v>
       </c>
       <c r="E24">
-        <v>26.54600000000001</v>
+        <v>30.63900000000002</v>
       </c>
       <c r="F24">
-        <v>90.04600000000001</v>
+        <v>94.13900000000001</v>
       </c>
       <c r="G24">
         <v>73.5</v>
@@ -3255,28 +3255,28 @@
         <v>62.4</v>
       </c>
       <c r="M24">
-        <v>4.5293138</v>
+        <v>4.735191700000001</v>
       </c>
       <c r="N24">
-        <v>57.8706862</v>
+        <v>57.6648083</v>
       </c>
       <c r="O24">
-        <v>14.46767155</v>
+        <v>14.416202075</v>
       </c>
       <c r="P24">
-        <v>43.40301465</v>
+        <v>43.248606225</v>
       </c>
       <c r="Q24">
-        <v>59.80301465</v>
+        <v>59.64860622499999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09293464310577224</v>
+        <v>0.09342046709160785</v>
       </c>
       <c r="T24">
-        <v>0.6858664890048766</v>
+        <v>0.6929358199573078</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>13.7769213517509</v>
+        <v>13.17792477123999</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08061050966053805</v>
+        <v>0.08070249769857377</v>
       </c>
       <c r="C25">
-        <v>339.537757843969</v>
+        <v>334.8988902691592</v>
       </c>
       <c r="D25">
-        <v>360.176757843969</v>
+        <v>359.6308902691592</v>
       </c>
       <c r="E25">
-        <v>30.63900000000002</v>
+        <v>34.73200000000002</v>
       </c>
       <c r="F25">
-        <v>94.13900000000001</v>
+        <v>98.23200000000001</v>
       </c>
       <c r="G25">
         <v>73.5</v>
@@ -3337,45 +3337,45 @@
         <v>62.4</v>
       </c>
       <c r="M25">
-        <v>4.735191700000001</v>
+        <v>5.088417600000001</v>
       </c>
       <c r="N25">
-        <v>57.6648083</v>
+        <v>57.3115824</v>
       </c>
       <c r="O25">
-        <v>14.416202075</v>
+        <v>14.3278956</v>
       </c>
       <c r="P25">
-        <v>43.248606225</v>
+        <v>42.9836868</v>
       </c>
       <c r="Q25">
-        <v>59.64860622499999</v>
+        <v>59.3836868</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09342046709160785</v>
+        <v>0.093919075919176</v>
       </c>
       <c r="T25">
-        <v>0.6929358199573078</v>
+        <v>0.7001911859348031</v>
       </c>
       <c r="U25">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V25">
         <v>0.25</v>
       </c>
       <c r="W25">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y25">
-        <v>13.17792477123999</v>
+        <v>12.26314444003181</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08070249769857377</v>
+        <v>0.08053573573660947</v>
       </c>
       <c r="C26">
-        <v>334.8988902691592</v>
+        <v>331.7966973601298</v>
       </c>
       <c r="D26">
-        <v>359.6308902691592</v>
+        <v>360.6216973601298</v>
       </c>
       <c r="E26">
-        <v>34.73200000000001</v>
+        <v>38.82500000000001</v>
       </c>
       <c r="F26">
-        <v>98.232</v>
+        <v>102.325</v>
       </c>
       <c r="G26">
         <v>73.5</v>
@@ -3419,28 +3419,28 @@
         <v>62.4</v>
       </c>
       <c r="M26">
-        <v>5.0884176</v>
+        <v>5.300435</v>
       </c>
       <c r="N26">
-        <v>57.3115824</v>
+        <v>57.099565</v>
       </c>
       <c r="O26">
-        <v>14.3278956</v>
+        <v>14.27489125</v>
       </c>
       <c r="P26">
-        <v>42.9836868</v>
+        <v>42.82467375</v>
       </c>
       <c r="Q26">
-        <v>59.3836868</v>
+        <v>59.22467375</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.093919075919176</v>
+        <v>0.09443098098214596</v>
       </c>
       <c r="T26">
-        <v>0.7001911859348031</v>
+        <v>0.7076400283383648</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>12.26314444003181</v>
+        <v>11.77261866243053</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08053573573660947</v>
+        <v>0.08036897377464518</v>
       </c>
       <c r="C27">
-        <v>331.7966973601298</v>
+        <v>328.6999790131338</v>
       </c>
       <c r="D27">
-        <v>360.6216973601298</v>
+        <v>361.6179790131338</v>
       </c>
       <c r="E27">
-        <v>38.82500000000001</v>
+        <v>42.91800000000001</v>
       </c>
       <c r="F27">
-        <v>102.325</v>
+        <v>106.418</v>
       </c>
       <c r="G27">
         <v>73.5</v>
@@ -3501,28 +3501,28 @@
         <v>62.4</v>
       </c>
       <c r="M27">
-        <v>5.300435</v>
+        <v>5.5124524</v>
       </c>
       <c r="N27">
-        <v>57.099565</v>
+        <v>56.8875476</v>
       </c>
       <c r="O27">
-        <v>14.27489125</v>
+        <v>14.2218869</v>
       </c>
       <c r="P27">
-        <v>42.82467375</v>
+        <v>42.6656607</v>
       </c>
       <c r="Q27">
-        <v>59.22467375</v>
+        <v>59.0656607</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09443098098214596</v>
+        <v>0.09495672131708807</v>
       </c>
       <c r="T27">
-        <v>0.7076400283383648</v>
+        <v>0.7152901908068877</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.77261866243053</v>
+        <v>11.31982563695244</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08036897377464518</v>
+        <v>0.08020221181268088</v>
       </c>
       <c r="C28">
-        <v>328.6999790131338</v>
+        <v>325.6087807272279</v>
       </c>
       <c r="D28">
-        <v>361.6179790131338</v>
+        <v>362.6197807272279</v>
       </c>
       <c r="E28">
-        <v>42.91800000000001</v>
+        <v>47.01100000000002</v>
       </c>
       <c r="F28">
-        <v>106.418</v>
+        <v>110.511</v>
       </c>
       <c r="G28">
         <v>73.5</v>
@@ -3583,28 +3583,28 @@
         <v>62.4</v>
       </c>
       <c r="M28">
-        <v>5.5124524</v>
+        <v>5.7244698</v>
       </c>
       <c r="N28">
-        <v>56.8875476</v>
+        <v>56.6755302</v>
       </c>
       <c r="O28">
-        <v>14.2218869</v>
+        <v>14.16888255</v>
       </c>
       <c r="P28">
-        <v>42.6656607</v>
+        <v>42.50664765</v>
       </c>
       <c r="Q28">
-        <v>59.0656607</v>
+        <v>58.90664765</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09495672131708807</v>
+        <v>0.09549686549682312</v>
       </c>
       <c r="T28">
-        <v>0.7152901908068877</v>
+        <v>0.7231499467676988</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.31982563695244</v>
+        <v>10.90057283558383</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08020221181268088</v>
+        <v>0.0800354498507166</v>
       </c>
       <c r="C29">
-        <v>325.6087807272279</v>
+        <v>322.523148507059</v>
       </c>
       <c r="D29">
-        <v>362.6197807272279</v>
+        <v>363.627148507059</v>
       </c>
       <c r="E29">
-        <v>47.01100000000002</v>
+        <v>51.10400000000002</v>
       </c>
       <c r="F29">
-        <v>110.511</v>
+        <v>114.604</v>
       </c>
       <c r="G29">
         <v>73.5</v>
@@ -3665,28 +3665,28 @@
         <v>62.4</v>
       </c>
       <c r="M29">
-        <v>5.7244698</v>
+        <v>5.9364872</v>
       </c>
       <c r="N29">
-        <v>56.6755302</v>
+        <v>56.4635128</v>
       </c>
       <c r="O29">
-        <v>14.16888255</v>
+        <v>14.1158782</v>
       </c>
       <c r="P29">
-        <v>42.50664765</v>
+        <v>42.3476346</v>
       </c>
       <c r="Q29">
-        <v>58.90664765</v>
+        <v>58.7476346</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.09549686549682312</v>
+        <v>0.09605201368155084</v>
       </c>
       <c r="T29">
-        <v>0.7231499467676988</v>
+        <v>0.731228029282977</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.90057283558383</v>
+        <v>10.51126666288441</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0800354498507166</v>
+        <v>0.07986868788875229</v>
       </c>
       <c r="C30">
-        <v>322.523148507059</v>
+        <v>319.4431288699074</v>
       </c>
       <c r="D30">
-        <v>363.627148507059</v>
+        <v>364.6401288699074</v>
       </c>
       <c r="E30">
-        <v>51.10400000000002</v>
+        <v>55.19700000000002</v>
       </c>
       <c r="F30">
-        <v>114.604</v>
+        <v>118.697</v>
       </c>
       <c r="G30">
         <v>73.5</v>
@@ -3747,28 +3747,28 @@
         <v>62.4</v>
       </c>
       <c r="M30">
-        <v>5.9364872</v>
+        <v>6.148504600000001</v>
       </c>
       <c r="N30">
-        <v>56.4635128</v>
+        <v>56.2514954</v>
       </c>
       <c r="O30">
-        <v>14.1158782</v>
+        <v>14.06287385</v>
       </c>
       <c r="P30">
-        <v>42.3476346</v>
+        <v>42.18862154999999</v>
       </c>
       <c r="Q30">
-        <v>58.7476346</v>
+        <v>58.58862154999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09605201368155084</v>
+        <v>0.0966227998433131</v>
       </c>
       <c r="T30">
-        <v>0.731228029282977</v>
+        <v>0.7395336634184038</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.51126666288441</v>
+        <v>10.14880919175046</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07986868788875229</v>
+        <v>0.08008442592678799</v>
       </c>
       <c r="C31">
-        <v>319.4431288699074</v>
+        <v>314.0407161066838</v>
       </c>
       <c r="D31">
-        <v>364.6401288699074</v>
+        <v>363.3307161066838</v>
       </c>
       <c r="E31">
-        <v>55.197</v>
+        <v>59.29</v>
       </c>
       <c r="F31">
-        <v>118.697</v>
+        <v>122.79</v>
       </c>
       <c r="G31">
         <v>73.5</v>
@@ -3829,45 +3829,45 @@
         <v>62.4</v>
       </c>
       <c r="M31">
-        <v>6.148504599999999</v>
+        <v>6.569265</v>
       </c>
       <c r="N31">
-        <v>56.2514954</v>
+        <v>55.830735</v>
       </c>
       <c r="O31">
-        <v>14.06287385</v>
+        <v>13.95768375</v>
       </c>
       <c r="P31">
-        <v>42.18862154999999</v>
+        <v>41.87305125</v>
       </c>
       <c r="Q31">
-        <v>58.58862154999999</v>
+        <v>58.27305124999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.0966227998433131</v>
+        <v>0.09720989418112572</v>
       </c>
       <c r="T31">
-        <v>0.7395336634184038</v>
+        <v>0.7480766013862713</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.25</v>
       </c>
       <c r="W31">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>10.14880919175046</v>
+        <v>9.498779543830246</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08008442592678799</v>
+        <v>0.07993041396482371</v>
       </c>
       <c r="C32">
-        <v>314.0407161066838</v>
+        <v>310.8815222181373</v>
       </c>
       <c r="D32">
-        <v>363.3307161066838</v>
+        <v>364.2645222181373</v>
       </c>
       <c r="E32">
-        <v>59.29</v>
+        <v>63.383</v>
       </c>
       <c r="F32">
-        <v>122.79</v>
+        <v>126.883</v>
       </c>
       <c r="G32">
         <v>73.5</v>
@@ -3911,28 +3911,28 @@
         <v>62.4</v>
       </c>
       <c r="M32">
-        <v>6.569265</v>
+        <v>6.7882405</v>
       </c>
       <c r="N32">
-        <v>55.830735</v>
+        <v>55.6117595</v>
       </c>
       <c r="O32">
-        <v>13.95768375</v>
+        <v>13.902939875</v>
       </c>
       <c r="P32">
-        <v>41.87305125</v>
+        <v>41.708819625</v>
       </c>
       <c r="Q32">
-        <v>58.27305124999999</v>
+        <v>58.108819625</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.09720989418112572</v>
+        <v>0.09781400574612133</v>
       </c>
       <c r="T32">
-        <v>0.7480766013862713</v>
+        <v>0.7568671607445119</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.498779543830246</v>
+        <v>9.192367300480884</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07993041396482371</v>
+        <v>0.07977640200285943</v>
       </c>
       <c r="C33">
-        <v>310.8815222181373</v>
+        <v>307.7271406987348</v>
       </c>
       <c r="D33">
-        <v>364.2645222181373</v>
+        <v>365.2031406987348</v>
       </c>
       <c r="E33">
-        <v>63.383</v>
+        <v>67.476</v>
       </c>
       <c r="F33">
-        <v>126.883</v>
+        <v>130.976</v>
       </c>
       <c r="G33">
         <v>73.5</v>
@@ -3993,28 +3993,28 @@
         <v>62.4</v>
       </c>
       <c r="M33">
-        <v>6.7882405</v>
+        <v>7.007216</v>
       </c>
       <c r="N33">
-        <v>55.6117595</v>
+        <v>55.392784</v>
       </c>
       <c r="O33">
-        <v>13.902939875</v>
+        <v>13.848196</v>
       </c>
       <c r="P33">
-        <v>41.708819625</v>
+        <v>41.544588</v>
       </c>
       <c r="Q33">
-        <v>58.108819625</v>
+        <v>57.944588</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.09781400574612133</v>
+        <v>0.09843588529832269</v>
       </c>
       <c r="T33">
-        <v>0.7568671607445119</v>
+        <v>0.7659162659662302</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>9.192367300480884</v>
+        <v>8.905105822340856</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07977640200285943</v>
+        <v>0.07962239004089512</v>
       </c>
       <c r="C34">
-        <v>307.7271406987348</v>
+        <v>304.577608845393</v>
       </c>
       <c r="D34">
-        <v>365.2031406987348</v>
+        <v>366.146608845393</v>
       </c>
       <c r="E34">
-        <v>67.476</v>
+        <v>71.56900000000002</v>
       </c>
       <c r="F34">
-        <v>130.976</v>
+        <v>135.069</v>
       </c>
       <c r="G34">
         <v>73.5</v>
@@ -4075,28 +4075,28 @@
         <v>62.4</v>
       </c>
       <c r="M34">
-        <v>7.007216</v>
+        <v>7.226191500000001</v>
       </c>
       <c r="N34">
-        <v>55.392784</v>
+        <v>55.1738085</v>
       </c>
       <c r="O34">
-        <v>13.848196</v>
+        <v>13.793452125</v>
       </c>
       <c r="P34">
-        <v>41.544588</v>
+        <v>41.380356375</v>
       </c>
       <c r="Q34">
-        <v>57.944588</v>
+        <v>57.780356375</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.09843588529832269</v>
+        <v>0.09907632841924646</v>
       </c>
       <c r="T34">
-        <v>0.7659162659662302</v>
+        <v>0.7752354937318803</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.905105822340856</v>
+        <v>8.635254130754769</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07962239004089512</v>
+        <v>0.07946837807893083</v>
       </c>
       <c r="C35">
-        <v>304.577608845393</v>
+        <v>301.4329643414385</v>
       </c>
       <c r="D35">
-        <v>366.146608845393</v>
+        <v>367.0949643414385</v>
       </c>
       <c r="E35">
-        <v>71.56900000000002</v>
+        <v>75.66200000000001</v>
       </c>
       <c r="F35">
-        <v>135.069</v>
+        <v>139.162</v>
       </c>
       <c r="G35">
         <v>73.5</v>
@@ -4157,28 +4157,28 @@
         <v>62.4</v>
       </c>
       <c r="M35">
-        <v>7.226191500000001</v>
+        <v>7.445167000000001</v>
       </c>
       <c r="N35">
-        <v>55.1738085</v>
+        <v>54.954833</v>
       </c>
       <c r="O35">
-        <v>13.793452125</v>
+        <v>13.73870825</v>
       </c>
       <c r="P35">
-        <v>41.380356375</v>
+        <v>41.21612475</v>
       </c>
       <c r="Q35">
-        <v>57.780356375</v>
+        <v>57.61612475</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.09907632841924646</v>
+        <v>0.09973617890747097</v>
       </c>
       <c r="T35">
-        <v>0.7752354937318803</v>
+        <v>0.7848371223389137</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.635254130754769</v>
+        <v>8.38127606808551</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07946837807893083</v>
+        <v>0.07931436611696654</v>
       </c>
       <c r="C36">
-        <v>301.4329643414385</v>
+        <v>298.2932452616262</v>
       </c>
       <c r="D36">
-        <v>367.0949643414385</v>
+        <v>368.0482452616262</v>
       </c>
       <c r="E36">
-        <v>75.66200000000001</v>
+        <v>79.75500000000002</v>
       </c>
       <c r="F36">
-        <v>139.162</v>
+        <v>143.255</v>
       </c>
       <c r="G36">
         <v>73.5</v>
@@ -4239,28 +4239,28 @@
         <v>62.4</v>
       </c>
       <c r="M36">
-        <v>7.445167000000001</v>
+        <v>7.664142500000001</v>
       </c>
       <c r="N36">
-        <v>54.954833</v>
+        <v>54.73585749999999</v>
       </c>
       <c r="O36">
-        <v>13.73870825</v>
+        <v>13.683964375</v>
       </c>
       <c r="P36">
-        <v>41.21612475</v>
+        <v>41.05189312499999</v>
       </c>
       <c r="Q36">
-        <v>57.61612475</v>
+        <v>57.45189312499999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.09973617890747097</v>
+        <v>0.1004163324876408</v>
       </c>
       <c r="T36">
-        <v>0.7848371223389137</v>
+        <v>0.7947341856723175</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.38127606808551</v>
+        <v>8.141811037568779</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07931436611696654</v>
+        <v>0.07916035415500225</v>
       </c>
       <c r="C37">
-        <v>298.2932452616262</v>
+        <v>295.1584900772345</v>
       </c>
       <c r="D37">
-        <v>368.0482452616262</v>
+        <v>369.0064900772345</v>
       </c>
       <c r="E37">
-        <v>79.75500000000002</v>
+        <v>83.84800000000001</v>
       </c>
       <c r="F37">
-        <v>143.255</v>
+        <v>147.348</v>
       </c>
       <c r="G37">
         <v>73.5</v>
@@ -4321,28 +4321,28 @@
         <v>62.4</v>
       </c>
       <c r="M37">
-        <v>7.664142500000001</v>
+        <v>7.883118000000001</v>
       </c>
       <c r="N37">
-        <v>54.73585749999999</v>
+        <v>54.516882</v>
       </c>
       <c r="O37">
-        <v>13.683964375</v>
+        <v>13.6292205</v>
       </c>
       <c r="P37">
-        <v>41.05189312499999</v>
+        <v>40.88766149999999</v>
       </c>
       <c r="Q37">
-        <v>57.45189312499999</v>
+        <v>57.28766149999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1004163324876408</v>
+        <v>0.101117740867191</v>
       </c>
       <c r="T37">
-        <v>0.7947341856723175</v>
+        <v>0.8049405322348899</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.141811037568779</v>
+        <v>7.915649619858537</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07916035415500226</v>
+        <v>0.07900634219303797</v>
       </c>
       <c r="C38">
-        <v>295.1584900772344</v>
+        <v>292.0287376612403</v>
       </c>
       <c r="D38">
-        <v>369.0064900772344</v>
+        <v>369.9697376612402</v>
       </c>
       <c r="E38">
-        <v>83.84799999999998</v>
+        <v>87.941</v>
       </c>
       <c r="F38">
-        <v>147.348</v>
+        <v>151.441</v>
       </c>
       <c r="G38">
         <v>73.5</v>
@@ -4403,28 +4403,28 @@
         <v>62.4</v>
       </c>
       <c r="M38">
-        <v>7.883117999999999</v>
+        <v>8.102093500000001</v>
       </c>
       <c r="N38">
-        <v>54.516882</v>
+        <v>54.2979065</v>
       </c>
       <c r="O38">
-        <v>13.6292205</v>
+        <v>13.574476625</v>
       </c>
       <c r="P38">
-        <v>40.8876615</v>
+        <v>40.72342987499999</v>
       </c>
       <c r="Q38">
-        <v>57.2876615</v>
+        <v>57.12342987499999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.101117740867191</v>
+        <v>0.1018414161794253</v>
       </c>
       <c r="T38">
-        <v>0.8049405322348899</v>
+        <v>0.8154708897994489</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.91564961985854</v>
+        <v>7.701713143646145</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07900634219303797</v>
+        <v>0.07908033023107366</v>
       </c>
       <c r="C39">
-        <v>292.0287376612403</v>
+        <v>287.4723623377166</v>
       </c>
       <c r="D39">
-        <v>369.9697376612402</v>
+        <v>369.5063623377166</v>
       </c>
       <c r="E39">
-        <v>87.941</v>
+        <v>92.03400000000002</v>
       </c>
       <c r="F39">
-        <v>151.441</v>
+        <v>155.534</v>
       </c>
       <c r="G39">
         <v>73.5</v>
@@ -4485,45 +4485,45 @@
         <v>62.4</v>
       </c>
       <c r="M39">
-        <v>8.102093500000001</v>
+        <v>8.445496200000001</v>
       </c>
       <c r="N39">
-        <v>54.2979065</v>
+        <v>53.9545038</v>
       </c>
       <c r="O39">
-        <v>13.574476625</v>
+        <v>13.48862595</v>
       </c>
       <c r="P39">
-        <v>40.72342987499999</v>
+        <v>40.46587785</v>
       </c>
       <c r="Q39">
-        <v>57.12342987499999</v>
+        <v>56.86587785</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1018414161794253</v>
+        <v>0.1025884358565704</v>
       </c>
       <c r="T39">
-        <v>0.8154708897994489</v>
+        <v>0.8263409363177034</v>
       </c>
       <c r="U39">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V39">
         <v>0.25</v>
       </c>
       <c r="W39">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y39">
-        <v>7.701713143646145</v>
+        <v>7.388553439879589</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.07908033023107366</v>
+        <v>0.07893231826910937</v>
       </c>
       <c r="C40">
-        <v>287.4723623377166</v>
+        <v>284.3075022203828</v>
       </c>
       <c r="D40">
-        <v>369.5063623377166</v>
+        <v>370.4345022203829</v>
       </c>
       <c r="E40">
-        <v>92.03400000000002</v>
+        <v>96.12700000000001</v>
       </c>
       <c r="F40">
-        <v>155.534</v>
+        <v>159.627</v>
       </c>
       <c r="G40">
         <v>73.5</v>
@@ -4567,28 +4567,28 @@
         <v>62.4</v>
       </c>
       <c r="M40">
-        <v>8.445496200000001</v>
+        <v>8.6677461</v>
       </c>
       <c r="N40">
-        <v>53.9545038</v>
+        <v>53.7322539</v>
       </c>
       <c r="O40">
-        <v>13.48862595</v>
+        <v>13.433063475</v>
       </c>
       <c r="P40">
-        <v>40.46587785</v>
+        <v>40.299190425</v>
       </c>
       <c r="Q40">
-        <v>56.86587785</v>
+        <v>56.699190425</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1025884358565704</v>
+        <v>0.1033599479821465</v>
       </c>
       <c r="T40">
-        <v>0.8263409363177034</v>
+        <v>0.8375673778037694</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.388553439879589</v>
+        <v>7.199103351677548</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07893231826910937</v>
+        <v>0.07878430630714509</v>
       </c>
       <c r="C41">
-        <v>284.3075022203828</v>
+        <v>281.1473165172672</v>
       </c>
       <c r="D41">
-        <v>370.4345022203829</v>
+        <v>371.3673165172672</v>
       </c>
       <c r="E41">
-        <v>96.12700000000001</v>
+        <v>100.22</v>
       </c>
       <c r="F41">
-        <v>159.627</v>
+        <v>163.72</v>
       </c>
       <c r="G41">
         <v>73.5</v>
@@ -4649,28 +4649,28 @@
         <v>62.4</v>
       </c>
       <c r="M41">
-        <v>8.6677461</v>
+        <v>8.889996000000002</v>
       </c>
       <c r="N41">
-        <v>53.7322539</v>
+        <v>53.510004</v>
       </c>
       <c r="O41">
-        <v>13.433063475</v>
+        <v>13.377501</v>
       </c>
       <c r="P41">
-        <v>40.299190425</v>
+        <v>40.132503</v>
       </c>
       <c r="Q41">
-        <v>56.699190425</v>
+        <v>56.532503</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1033599479821465</v>
+        <v>0.1041571771785751</v>
       </c>
       <c r="T41">
-        <v>0.8375673778037694</v>
+        <v>0.8491680340060377</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.199103351677548</v>
+        <v>7.019125767885608</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07878430630714509</v>
+        <v>0.0786362943451808</v>
       </c>
       <c r="C42">
-        <v>281.1473165172672</v>
+        <v>277.9918406303226</v>
       </c>
       <c r="D42">
-        <v>371.3673165172672</v>
+        <v>372.3048406303226</v>
       </c>
       <c r="E42">
-        <v>100.22</v>
+        <v>104.313</v>
       </c>
       <c r="F42">
-        <v>163.72</v>
+        <v>167.813</v>
       </c>
       <c r="G42">
         <v>73.5</v>
@@ -4731,28 +4731,28 @@
         <v>62.4</v>
       </c>
       <c r="M42">
-        <v>8.889996000000002</v>
+        <v>9.112245900000001</v>
       </c>
       <c r="N42">
-        <v>53.510004</v>
+        <v>53.2877541</v>
       </c>
       <c r="O42">
-        <v>13.377501</v>
+        <v>13.321938525</v>
       </c>
       <c r="P42">
-        <v>40.132503</v>
+        <v>39.965815575</v>
       </c>
       <c r="Q42">
-        <v>56.532503</v>
+        <v>56.365815575</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1041571771785751</v>
+        <v>0.1049814310935268</v>
       </c>
       <c r="T42">
-        <v>0.8491680340060377</v>
+        <v>0.8611619327914338</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.019125767885608</v>
+        <v>6.847927578424985</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0786362943451808</v>
+        <v>0.07848828238321651</v>
       </c>
       <c r="C43">
-        <v>277.9918406303226</v>
+        <v>274.8411103198978</v>
       </c>
       <c r="D43">
-        <v>372.3048406303226</v>
+        <v>373.2471103198978</v>
       </c>
       <c r="E43">
-        <v>104.313</v>
+        <v>108.406</v>
       </c>
       <c r="F43">
-        <v>167.813</v>
+        <v>171.906</v>
       </c>
       <c r="G43">
         <v>73.5</v>
@@ -4813,28 +4813,28 @@
         <v>62.4</v>
       </c>
       <c r="M43">
-        <v>9.112245900000001</v>
+        <v>9.334495800000003</v>
       </c>
       <c r="N43">
-        <v>53.2877541</v>
+        <v>53.06550419999999</v>
       </c>
       <c r="O43">
-        <v>13.321938525</v>
+        <v>13.26637605</v>
       </c>
       <c r="P43">
-        <v>39.965815575</v>
+        <v>39.79912814999999</v>
       </c>
       <c r="Q43">
-        <v>56.365815575</v>
+        <v>56.19912814999999</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1049814310935268</v>
+        <v>0.1058341075572698</v>
       </c>
       <c r="T43">
-        <v>0.8611619327914338</v>
+        <v>0.8735694142935676</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.847927578424985</v>
+        <v>6.684881683700579</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07848828238321651</v>
+        <v>0.07834027042125222</v>
       </c>
       <c r="C44">
-        <v>274.8411103198978</v>
+        <v>271.6951617092855</v>
       </c>
       <c r="D44">
-        <v>373.2471103198978</v>
+        <v>374.1941617092855</v>
       </c>
       <c r="E44">
-        <v>108.406</v>
+        <v>112.499</v>
       </c>
       <c r="F44">
-        <v>171.906</v>
+        <v>175.999</v>
       </c>
       <c r="G44">
         <v>73.5</v>
@@ -4895,28 +4895,28 @@
         <v>62.4</v>
       </c>
       <c r="M44">
-        <v>9.334495800000001</v>
+        <v>9.5567457</v>
       </c>
       <c r="N44">
-        <v>53.0655042</v>
+        <v>52.8432543</v>
       </c>
       <c r="O44">
-        <v>13.26637605</v>
+        <v>13.210813575</v>
       </c>
       <c r="P44">
-        <v>39.79912815</v>
+        <v>39.632440725</v>
       </c>
       <c r="Q44">
-        <v>56.19912815</v>
+        <v>56.03244072499999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1058341075572698</v>
+        <v>0.1067167024934249</v>
       </c>
       <c r="T44">
-        <v>0.8735694142935676</v>
+        <v>0.8864122460238464</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.68488168370058</v>
+        <v>6.529419318963358</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.07834027042125222</v>
+        <v>0.07819225845928793</v>
       </c>
       <c r="C45">
-        <v>271.6951617092855</v>
+        <v>268.5540312893374</v>
       </c>
       <c r="D45">
-        <v>374.1941617092855</v>
+        <v>375.1460312893374</v>
       </c>
       <c r="E45">
-        <v>112.499</v>
+        <v>116.592</v>
       </c>
       <c r="F45">
-        <v>175.999</v>
+        <v>180.092</v>
       </c>
       <c r="G45">
         <v>73.5</v>
@@ -4977,28 +4977,28 @@
         <v>62.4</v>
       </c>
       <c r="M45">
-        <v>9.5567457</v>
+        <v>9.7789956</v>
       </c>
       <c r="N45">
-        <v>52.8432543</v>
+        <v>52.6210044</v>
       </c>
       <c r="O45">
-        <v>13.210813575</v>
+        <v>13.1552511</v>
       </c>
       <c r="P45">
-        <v>39.632440725</v>
+        <v>39.4657533</v>
       </c>
       <c r="Q45">
-        <v>56.03244072499999</v>
+        <v>55.86575329999999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1067167024934249</v>
+        <v>0.1076308186772999</v>
       </c>
       <c r="T45">
-        <v>0.8864122460238464</v>
+        <v>0.899713750315921</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.529419318963358</v>
+        <v>6.381023425350554</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07819225845928793</v>
+        <v>0.07804424649732362</v>
       </c>
       <c r="C46">
-        <v>268.5540312893374</v>
+        <v>265.4177559231524</v>
       </c>
       <c r="D46">
-        <v>375.1460312893374</v>
+        <v>376.1027559231524</v>
       </c>
       <c r="E46">
-        <v>116.592</v>
+        <v>120.685</v>
       </c>
       <c r="F46">
-        <v>180.092</v>
+        <v>184.185</v>
       </c>
       <c r="G46">
         <v>73.5</v>
@@ -5059,28 +5059,28 @@
         <v>62.4</v>
       </c>
       <c r="M46">
-        <v>9.7789956</v>
+        <v>10.0012455</v>
       </c>
       <c r="N46">
-        <v>52.6210044</v>
+        <v>52.3987545</v>
       </c>
       <c r="O46">
-        <v>13.1552511</v>
+        <v>13.099688625</v>
       </c>
       <c r="P46">
-        <v>39.4657533</v>
+        <v>39.299065875</v>
       </c>
       <c r="Q46">
-        <v>55.86575329999999</v>
+        <v>55.699065875</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1076308186772999</v>
+        <v>0.1085781754496793</v>
       </c>
       <c r="T46">
-        <v>0.899713750315921</v>
+        <v>0.9134989456731618</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.381023425350554</v>
+        <v>6.239222904787209</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07804424649732362</v>
+        <v>0.07824123453535933</v>
       </c>
       <c r="C47">
-        <v>265.4177559231524</v>
+        <v>260.0525289615902</v>
       </c>
       <c r="D47">
-        <v>376.1027559231524</v>
+        <v>374.8305289615902</v>
       </c>
       <c r="E47">
-        <v>120.685</v>
+        <v>124.778</v>
       </c>
       <c r="F47">
-        <v>184.185</v>
+        <v>188.278</v>
       </c>
       <c r="G47">
         <v>73.5</v>
@@ -5141,45 +5141,45 @@
         <v>62.4</v>
       </c>
       <c r="M47">
-        <v>10.0012455</v>
+        <v>10.4117734</v>
       </c>
       <c r="N47">
-        <v>52.3987545</v>
+        <v>51.9882266</v>
       </c>
       <c r="O47">
-        <v>13.099688625</v>
+        <v>12.99705665</v>
       </c>
       <c r="P47">
-        <v>39.299065875</v>
+        <v>38.99116995</v>
       </c>
       <c r="Q47">
-        <v>55.699065875</v>
+        <v>55.39116995</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1085781754496793</v>
+        <v>0.1095606195099247</v>
       </c>
       <c r="T47">
-        <v>0.9134989456731618</v>
+        <v>0.9277947038214116</v>
       </c>
       <c r="U47">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V47">
         <v>0.25</v>
       </c>
       <c r="W47">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y47">
-        <v>6.239222904787209</v>
+        <v>5.993215334478946</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07824123453535933</v>
+        <v>0.07810072257339505</v>
       </c>
       <c r="C48">
-        <v>260.0525289615902</v>
+        <v>256.8661287948288</v>
       </c>
       <c r="D48">
-        <v>374.8305289615902</v>
+        <v>375.7371287948288</v>
       </c>
       <c r="E48">
-        <v>124.778</v>
+        <v>128.871</v>
       </c>
       <c r="F48">
-        <v>188.278</v>
+        <v>192.371</v>
       </c>
       <c r="G48">
         <v>73.5</v>
@@ -5223,28 +5223,28 @@
         <v>62.4</v>
       </c>
       <c r="M48">
-        <v>10.4117734</v>
+        <v>10.6381163</v>
       </c>
       <c r="N48">
-        <v>51.9882266</v>
+        <v>51.7618837</v>
       </c>
       <c r="O48">
-        <v>12.99705665</v>
+        <v>12.940470925</v>
       </c>
       <c r="P48">
-        <v>38.99116995</v>
+        <v>38.821412775</v>
       </c>
       <c r="Q48">
-        <v>55.39116995</v>
+        <v>55.221412775</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1095606195099247</v>
+        <v>0.110580136930934</v>
       </c>
       <c r="T48">
-        <v>0.9277947038214116</v>
+        <v>0.9426299245412935</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.993215334478946</v>
+        <v>5.865700114596415</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.07810072257339505</v>
+        <v>0.07796021061143076</v>
       </c>
       <c r="C49">
-        <v>256.8661287948288</v>
+        <v>253.6841248337853</v>
       </c>
       <c r="D49">
-        <v>375.7371287948288</v>
+        <v>376.6481248337853</v>
       </c>
       <c r="E49">
-        <v>128.871</v>
+        <v>132.964</v>
       </c>
       <c r="F49">
-        <v>192.371</v>
+        <v>196.464</v>
       </c>
       <c r="G49">
         <v>73.5</v>
@@ -5305,28 +5305,28 @@
         <v>62.4</v>
       </c>
       <c r="M49">
-        <v>10.6381163</v>
+        <v>10.8644592</v>
       </c>
       <c r="N49">
-        <v>51.7618837</v>
+        <v>51.53554079999999</v>
       </c>
       <c r="O49">
-        <v>12.940470925</v>
+        <v>12.8838852</v>
       </c>
       <c r="P49">
-        <v>38.821412775</v>
+        <v>38.6516556</v>
       </c>
       <c r="Q49">
-        <v>55.221412775</v>
+        <v>55.0516556</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.110580136930934</v>
+        <v>0.1116388665604438</v>
       </c>
       <c r="T49">
-        <v>0.9426299245412935</v>
+        <v>0.9580357306734785</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.865700114596415</v>
+        <v>5.743498028875655</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.07796021061143076</v>
+        <v>0.07781969864946646</v>
       </c>
       <c r="C50">
-        <v>253.6841248337853</v>
+        <v>250.5065491327294</v>
       </c>
       <c r="D50">
-        <v>376.6481248337853</v>
+        <v>377.5635491327294</v>
       </c>
       <c r="E50">
-        <v>132.964</v>
+        <v>137.057</v>
       </c>
       <c r="F50">
-        <v>196.464</v>
+        <v>200.557</v>
       </c>
       <c r="G50">
         <v>73.5</v>
@@ -5387,28 +5387,28 @@
         <v>62.4</v>
       </c>
       <c r="M50">
-        <v>10.8644592</v>
+        <v>11.0908021</v>
       </c>
       <c r="N50">
-        <v>51.5355408</v>
+        <v>51.3091979</v>
       </c>
       <c r="O50">
-        <v>12.8838852</v>
+        <v>12.827299475</v>
       </c>
       <c r="P50">
-        <v>38.6516556</v>
+        <v>38.481898425</v>
       </c>
       <c r="Q50">
-        <v>55.0516556</v>
+        <v>54.881898425</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1116388665604438</v>
+        <v>0.1127391149989538</v>
       </c>
       <c r="T50">
-        <v>0.9580357306734785</v>
+        <v>0.9740456860657492</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.743498028875657</v>
+        <v>5.626283783388399</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.07781969864946646</v>
+        <v>0.07767918668750218</v>
       </c>
       <c r="C51">
-        <v>250.5065491327294</v>
+        <v>247.3334340583152</v>
       </c>
       <c r="D51">
-        <v>377.5635491327294</v>
+        <v>378.4834340583152</v>
       </c>
       <c r="E51">
-        <v>137.057</v>
+        <v>141.15</v>
       </c>
       <c r="F51">
-        <v>200.557</v>
+        <v>204.65</v>
       </c>
       <c r="G51">
         <v>73.5</v>
@@ -5469,28 +5469,28 @@
         <v>62.4</v>
       </c>
       <c r="M51">
-        <v>11.0908021</v>
+        <v>11.317145</v>
       </c>
       <c r="N51">
-        <v>51.3091979</v>
+        <v>51.082855</v>
       </c>
       <c r="O51">
-        <v>12.827299475</v>
+        <v>12.77071375</v>
       </c>
       <c r="P51">
-        <v>38.481898425</v>
+        <v>38.31214125</v>
       </c>
       <c r="Q51">
-        <v>54.881898425</v>
+        <v>54.71214124999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1127391149989538</v>
+        <v>0.1138833733750043</v>
       </c>
       <c r="T51">
-        <v>0.9740456860657492</v>
+        <v>0.9906960396737107</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.626283783388399</v>
+        <v>5.513758107720631</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.07767918668750218</v>
+        <v>0.07753867472553787</v>
       </c>
       <c r="C52">
-        <v>247.3334340583152</v>
+        <v>244.1648122933963</v>
       </c>
       <c r="D52">
-        <v>378.4834340583152</v>
+        <v>379.4078122933963</v>
       </c>
       <c r="E52">
-        <v>141.15</v>
+        <v>145.243</v>
       </c>
       <c r="F52">
-        <v>204.65</v>
+        <v>208.743</v>
       </c>
       <c r="G52">
         <v>73.5</v>
@@ -5551,28 +5551,28 @@
         <v>62.4</v>
       </c>
       <c r="M52">
-        <v>11.317145</v>
+        <v>11.5434879</v>
       </c>
       <c r="N52">
-        <v>51.082855</v>
+        <v>50.8565121</v>
       </c>
       <c r="O52">
-        <v>12.77071375</v>
+        <v>12.714128025</v>
       </c>
       <c r="P52">
-        <v>38.31214125</v>
+        <v>38.142384075</v>
       </c>
       <c r="Q52">
-        <v>54.71214124999999</v>
+        <v>54.54238407499999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1138833733750043</v>
+        <v>0.1150743361745671</v>
       </c>
       <c r="T52">
-        <v>0.9906960396737107</v>
+        <v>1.008025999551385</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.513758107720631</v>
+        <v>5.405645203647676</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.07753867472553787</v>
+        <v>0.07739816276357357</v>
       </c>
       <c r="C53">
-        <v>244.1648122933963</v>
+        <v>241.0007168408955</v>
       </c>
       <c r="D53">
-        <v>379.4078122933963</v>
+        <v>380.3367168408955</v>
       </c>
       <c r="E53">
-        <v>145.243</v>
+        <v>149.336</v>
       </c>
       <c r="F53">
-        <v>208.743</v>
+        <v>212.836</v>
       </c>
       <c r="G53">
         <v>73.5</v>
@@ -5633,28 +5633,28 @@
         <v>62.4</v>
       </c>
       <c r="M53">
-        <v>11.5434879</v>
+        <v>11.7698308</v>
       </c>
       <c r="N53">
-        <v>50.8565121</v>
+        <v>50.6301692</v>
       </c>
       <c r="O53">
-        <v>12.714128025</v>
+        <v>12.6575423</v>
       </c>
       <c r="P53">
-        <v>38.142384075</v>
+        <v>37.97262689999999</v>
       </c>
       <c r="Q53">
-        <v>54.54238407499999</v>
+        <v>54.37262689999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1150743361745671</v>
+        <v>0.1163149224241116</v>
       </c>
       <c r="T53">
-        <v>1.008025999551385</v>
+        <v>1.026078041090629</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.405645203647676</v>
+        <v>5.301690488192913</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.07739816276357357</v>
+        <v>0.07725765080160929</v>
       </c>
       <c r="C54">
-        <v>241.0007168408955</v>
+        <v>237.8411810277335</v>
       </c>
       <c r="D54">
-        <v>380.3367168408955</v>
+        <v>381.2701810277335</v>
       </c>
       <c r="E54">
-        <v>149.336</v>
+        <v>153.429</v>
       </c>
       <c r="F54">
-        <v>212.836</v>
+        <v>216.929</v>
       </c>
       <c r="G54">
         <v>73.5</v>
@@ -5715,28 +5715,28 @@
         <v>62.4</v>
       </c>
       <c r="M54">
-        <v>11.7698308</v>
+        <v>11.9961737</v>
       </c>
       <c r="N54">
-        <v>50.6301692</v>
+        <v>50.4038263</v>
       </c>
       <c r="O54">
-        <v>12.6575423</v>
+        <v>12.600956575</v>
       </c>
       <c r="P54">
-        <v>37.97262689999999</v>
+        <v>37.802869725</v>
       </c>
       <c r="Q54">
-        <v>54.37262689999999</v>
+        <v>54.202869725</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1163149224241116</v>
+        <v>0.1176082995778921</v>
       </c>
       <c r="T54">
-        <v>1.026078041090629</v>
+        <v>1.044898254610266</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.301690488192913</v>
+        <v>5.201658592189274</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.07725765080160929</v>
+        <v>0.07711713883964499</v>
       </c>
       <c r="C55">
-        <v>237.8411810277335</v>
+        <v>234.6862385088147</v>
       </c>
       <c r="D55">
-        <v>381.2701810277335</v>
+        <v>382.2082385088148</v>
       </c>
       <c r="E55">
-        <v>153.429</v>
+        <v>157.522</v>
       </c>
       <c r="F55">
-        <v>216.929</v>
+        <v>221.022</v>
       </c>
       <c r="G55">
         <v>73.5</v>
@@ -5797,28 +5797,28 @@
         <v>62.4</v>
       </c>
       <c r="M55">
-        <v>11.9961737</v>
+        <v>12.2225166</v>
       </c>
       <c r="N55">
-        <v>50.4038263</v>
+        <v>50.1774834</v>
       </c>
       <c r="O55">
-        <v>12.600956575</v>
+        <v>12.54437085</v>
       </c>
       <c r="P55">
-        <v>37.802869725</v>
+        <v>37.63311255</v>
       </c>
       <c r="Q55">
-        <v>54.202869725</v>
+        <v>54.03311255</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1176082995778921</v>
+        <v>0.1189579105209674</v>
       </c>
       <c r="T55">
-        <v>1.044898254610266</v>
+        <v>1.064536738282931</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.201658592189274</v>
+        <v>5.105331581222806</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.07711713883964499</v>
+        <v>0.07697662687768071</v>
       </c>
       <c r="C56">
-        <v>234.6862385088147</v>
+        <v>231.5359232710711</v>
       </c>
       <c r="D56">
-        <v>382.2082385088148</v>
+        <v>383.1509232710711</v>
       </c>
       <c r="E56">
-        <v>157.522</v>
+        <v>161.615</v>
       </c>
       <c r="F56">
-        <v>221.022</v>
+        <v>225.115</v>
       </c>
       <c r="G56">
         <v>73.5</v>
@@ -5879,28 +5879,28 @@
         <v>62.4</v>
       </c>
       <c r="M56">
-        <v>12.2225166</v>
+        <v>12.4488595</v>
       </c>
       <c r="N56">
-        <v>50.1774834</v>
+        <v>49.95114049999999</v>
       </c>
       <c r="O56">
-        <v>12.54437085</v>
+        <v>12.487785125</v>
       </c>
       <c r="P56">
-        <v>37.63311255</v>
+        <v>37.46335537499999</v>
       </c>
       <c r="Q56">
-        <v>54.03311255</v>
+        <v>53.86335537499999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1189579105209674</v>
+        <v>0.1203675041726238</v>
       </c>
       <c r="T56">
-        <v>1.064536738282931</v>
+        <v>1.085048043452159</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.105331581222806</v>
+        <v>5.012507370655118</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.07697662687768071</v>
+        <v>0.0768361149157164</v>
       </c>
       <c r="C57">
-        <v>231.5359232710711</v>
+        <v>228.3902696375679</v>
       </c>
       <c r="D57">
-        <v>383.1509232710711</v>
+        <v>384.0982696375679</v>
       </c>
       <c r="E57">
-        <v>161.615</v>
+        <v>165.708</v>
       </c>
       <c r="F57">
-        <v>225.115</v>
+        <v>229.208</v>
       </c>
       <c r="G57">
         <v>73.5</v>
@@ -5961,28 +5961,28 @@
         <v>62.4</v>
       </c>
       <c r="M57">
-        <v>12.4488595</v>
+        <v>12.6752024</v>
       </c>
       <c r="N57">
-        <v>49.95114049999999</v>
+        <v>49.7247976</v>
       </c>
       <c r="O57">
-        <v>12.487785125</v>
+        <v>12.4311994</v>
       </c>
       <c r="P57">
-        <v>37.46335537499999</v>
+        <v>37.2935982</v>
       </c>
       <c r="Q57">
-        <v>53.86335537499999</v>
+        <v>53.6935982</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1203675041726238</v>
+        <v>0.1218411702629918</v>
       </c>
       <c r="T57">
-        <v>1.085048043452159</v>
+        <v>1.106491680674534</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.012507370655118</v>
+        <v>4.922998310464848</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.0768361149157164</v>
+        <v>0.07669560295375212</v>
       </c>
       <c r="C58">
-        <v>228.3902696375679</v>
+        <v>225.249312271668</v>
       </c>
       <c r="D58">
-        <v>384.0982696375679</v>
+        <v>385.0503122716681</v>
       </c>
       <c r="E58">
-        <v>165.708</v>
+        <v>169.801</v>
       </c>
       <c r="F58">
-        <v>229.208</v>
+        <v>233.301</v>
       </c>
       <c r="G58">
         <v>73.5</v>
@@ -6043,28 +6043,28 @@
         <v>62.4</v>
       </c>
       <c r="M58">
-        <v>12.6752024</v>
+        <v>12.9015453</v>
       </c>
       <c r="N58">
-        <v>49.7247976</v>
+        <v>49.4984547</v>
       </c>
       <c r="O58">
-        <v>12.4311994</v>
+        <v>12.374613675</v>
       </c>
       <c r="P58">
-        <v>37.2935982</v>
+        <v>37.123841025</v>
       </c>
       <c r="Q58">
-        <v>53.6935982</v>
+        <v>53.523841025</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1218411702629918</v>
+        <v>0.1233833789622142</v>
       </c>
       <c r="T58">
-        <v>1.106491680674534</v>
+        <v>1.128932696372368</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.922998310464848</v>
+        <v>4.836629919053184</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.07669560295375212</v>
+        <v>0.07655509099178784</v>
       </c>
       <c r="C59">
-        <v>225.249312271668</v>
+        <v>222.1130861812619</v>
       </c>
       <c r="D59">
-        <v>385.0503122716681</v>
+        <v>386.007086181262</v>
       </c>
       <c r="E59">
-        <v>169.801</v>
+        <v>173.894</v>
       </c>
       <c r="F59">
-        <v>233.301</v>
+        <v>237.394</v>
       </c>
       <c r="G59">
         <v>73.5</v>
@@ -6125,28 +6125,28 @@
         <v>62.4</v>
       </c>
       <c r="M59">
-        <v>12.9015453</v>
+        <v>13.1278882</v>
       </c>
       <c r="N59">
-        <v>49.4984547</v>
+        <v>49.2721118</v>
       </c>
       <c r="O59">
-        <v>12.374613675</v>
+        <v>12.31802795</v>
       </c>
       <c r="P59">
-        <v>37.123841025</v>
+        <v>36.95408385</v>
       </c>
       <c r="Q59">
-        <v>53.523841025</v>
+        <v>53.35408384999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1233833789622142</v>
+        <v>0.1249990261709234</v>
       </c>
       <c r="T59">
-        <v>1.128932696372368</v>
+        <v>1.152442331865337</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.836629919053184</v>
+        <v>4.753239748035026</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.07655509099178784</v>
+        <v>0.07641457902982354</v>
       </c>
       <c r="C60">
-        <v>222.113086181262</v>
+        <v>218.9816267230568</v>
       </c>
       <c r="D60">
-        <v>386.007086181262</v>
+        <v>386.9686267230568</v>
       </c>
       <c r="E60">
-        <v>173.894</v>
+        <v>177.987</v>
       </c>
       <c r="F60">
-        <v>237.394</v>
+        <v>241.487</v>
       </c>
       <c r="G60">
         <v>73.5</v>
@@ -6207,28 +6207,28 @@
         <v>62.4</v>
       </c>
       <c r="M60">
-        <v>13.1278882</v>
+        <v>13.3542311</v>
       </c>
       <c r="N60">
-        <v>49.2721118</v>
+        <v>49.0457689</v>
       </c>
       <c r="O60">
-        <v>12.31802795</v>
+        <v>12.261442225</v>
       </c>
       <c r="P60">
-        <v>36.95408385</v>
+        <v>36.784326675</v>
       </c>
       <c r="Q60">
-        <v>53.35408384999999</v>
+        <v>53.184326675</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1249990261709234</v>
+        <v>0.126693485438594</v>
       </c>
       <c r="T60">
-        <v>1.152442331865337</v>
+        <v>1.177098778845768</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.753239748035027</v>
+        <v>4.67267636247511</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.07641457902982354</v>
+        <v>0.07627406706785925</v>
       </c>
       <c r="C61">
-        <v>218.9816267230568</v>
+        <v>215.8549696069331</v>
       </c>
       <c r="D61">
-        <v>386.9686267230568</v>
+        <v>387.9349696069331</v>
       </c>
       <c r="E61">
-        <v>177.987</v>
+        <v>182.08</v>
       </c>
       <c r="F61">
-        <v>241.487</v>
+        <v>245.58</v>
       </c>
       <c r="G61">
         <v>73.5</v>
@@ -6289,28 +6289,28 @@
         <v>62.4</v>
       </c>
       <c r="M61">
-        <v>13.3542311</v>
+        <v>13.580574</v>
       </c>
       <c r="N61">
-        <v>49.0457689</v>
+        <v>48.819426</v>
       </c>
       <c r="O61">
-        <v>12.261442225</v>
+        <v>12.2048565</v>
       </c>
       <c r="P61">
-        <v>36.784326675</v>
+        <v>36.6145695</v>
       </c>
       <c r="Q61">
-        <v>53.184326675</v>
+        <v>53.0145695</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.126693485438594</v>
+        <v>0.1284726676696481</v>
       </c>
       <c r="T61">
-        <v>1.177098778845768</v>
+        <v>1.20298804817522</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.67267636247511</v>
+        <v>4.594798423100526</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.07627406706785925</v>
+        <v>0.07613355510589496</v>
       </c>
       <c r="C62">
-        <v>215.8549696069331</v>
+        <v>212.7331509003644</v>
       </c>
       <c r="D62">
-        <v>387.9349696069331</v>
+        <v>388.9061509003644</v>
       </c>
       <c r="E62">
-        <v>182.08</v>
+        <v>186.173</v>
       </c>
       <c r="F62">
-        <v>245.58</v>
+        <v>249.673</v>
       </c>
       <c r="G62">
         <v>73.5</v>
@@ -6371,28 +6371,28 @@
         <v>62.4</v>
       </c>
       <c r="M62">
-        <v>13.580574</v>
+        <v>13.8069169</v>
       </c>
       <c r="N62">
-        <v>48.819426</v>
+        <v>48.5930831</v>
       </c>
       <c r="O62">
-        <v>12.2048565</v>
+        <v>12.148270775</v>
       </c>
       <c r="P62">
-        <v>36.6145695</v>
+        <v>36.444812325</v>
       </c>
       <c r="Q62">
-        <v>53.0145695</v>
+        <v>52.844812325</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1284726676696481</v>
+        <v>0.1303430900151153</v>
       </c>
       <c r="T62">
-        <v>1.20298804817522</v>
+        <v>1.23020497234208</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.594798423100526</v>
+        <v>4.519473858787402</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.07613355510589496</v>
+        <v>0.07715554314393067</v>
       </c>
       <c r="C63">
-        <v>212.7331509003644</v>
+        <v>201.6853933917947</v>
       </c>
       <c r="D63">
-        <v>388.9061509003644</v>
+        <v>381.9513933917947</v>
       </c>
       <c r="E63">
-        <v>186.173</v>
+        <v>190.266</v>
       </c>
       <c r="F63">
-        <v>249.673</v>
+        <v>253.766</v>
       </c>
       <c r="G63">
         <v>73.5</v>
@@ -6453,45 +6453,45 @@
         <v>62.4</v>
       </c>
       <c r="M63">
-        <v>13.8069169</v>
+        <v>14.6676748</v>
       </c>
       <c r="N63">
-        <v>48.5930831</v>
+        <v>47.7323252</v>
       </c>
       <c r="O63">
-        <v>12.148270775</v>
+        <v>11.9330813</v>
       </c>
       <c r="P63">
-        <v>36.444812325</v>
+        <v>35.7992439</v>
       </c>
       <c r="Q63">
-        <v>52.844812325</v>
+        <v>52.1992439</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1303430900151153</v>
+        <v>0.1323119556419228</v>
       </c>
       <c r="T63">
-        <v>1.23020497234208</v>
+        <v>1.258854366201933</v>
       </c>
       <c r="U63">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V63">
         <v>0.25</v>
       </c>
       <c r="W63">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y63">
-        <v>4.519473858787402</v>
+        <v>4.254253032662</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.07715554314393067</v>
+        <v>0.07703378118196638</v>
       </c>
       <c r="C64">
-        <v>201.6853933917947</v>
+        <v>198.4079186206711</v>
       </c>
       <c r="D64">
-        <v>381.9513933917947</v>
+        <v>382.7669186206711</v>
       </c>
       <c r="E64">
-        <v>190.266</v>
+        <v>194.359</v>
       </c>
       <c r="F64">
-        <v>253.766</v>
+        <v>257.859</v>
       </c>
       <c r="G64">
         <v>73.5</v>
@@ -6535,28 +6535,28 @@
         <v>62.4</v>
       </c>
       <c r="M64">
-        <v>14.6676748</v>
+        <v>14.9042502</v>
       </c>
       <c r="N64">
-        <v>47.7323252</v>
+        <v>47.4957498</v>
       </c>
       <c r="O64">
-        <v>11.9330813</v>
+        <v>11.87393745</v>
       </c>
       <c r="P64">
-        <v>35.7992439</v>
+        <v>35.62181235</v>
       </c>
       <c r="Q64">
-        <v>52.1992439</v>
+        <v>52.02181235</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1323119556419228</v>
+        <v>0.134387246437747</v>
       </c>
       <c r="T64">
-        <v>1.258854366201933</v>
+        <v>1.289052375946102</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.254253032662</v>
+        <v>4.186725206746729</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.07703378118196638</v>
+        <v>0.07691201922000208</v>
       </c>
       <c r="C65">
-        <v>198.4079186206711</v>
+        <v>195.1339338459216</v>
       </c>
       <c r="D65">
-        <v>382.7669186206711</v>
+        <v>383.5859338459216</v>
       </c>
       <c r="E65">
-        <v>194.359</v>
+        <v>198.452</v>
       </c>
       <c r="F65">
-        <v>257.859</v>
+        <v>261.952</v>
       </c>
       <c r="G65">
         <v>73.5</v>
@@ -6617,28 +6617,28 @@
         <v>62.4</v>
       </c>
       <c r="M65">
-        <v>14.9042502</v>
+        <v>15.1408256</v>
       </c>
       <c r="N65">
-        <v>47.4957498</v>
+        <v>47.2591744</v>
       </c>
       <c r="O65">
-        <v>11.87393745</v>
+        <v>11.8147936</v>
       </c>
       <c r="P65">
-        <v>35.62181235</v>
+        <v>35.4443808</v>
       </c>
       <c r="Q65">
-        <v>52.02181235</v>
+        <v>51.8443808</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.134387246437747</v>
+        <v>0.1365778311666725</v>
       </c>
       <c r="T65">
-        <v>1.289052375946102</v>
+        <v>1.320928052898281</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.186725206746729</v>
+        <v>4.121307625391312</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.07691201922000208</v>
+        <v>0.0767902572580378</v>
       </c>
       <c r="C66">
-        <v>195.1339338459216</v>
+        <v>191.8634615184624</v>
       </c>
       <c r="D66">
-        <v>383.5859338459216</v>
+        <v>384.4084615184624</v>
       </c>
       <c r="E66">
-        <v>198.452</v>
+        <v>202.545</v>
       </c>
       <c r="F66">
-        <v>261.952</v>
+        <v>266.045</v>
       </c>
       <c r="G66">
         <v>73.5</v>
@@ -6699,28 +6699,28 @@
         <v>62.4</v>
       </c>
       <c r="M66">
-        <v>15.1408256</v>
+        <v>15.377401</v>
       </c>
       <c r="N66">
-        <v>47.2591744</v>
+        <v>47.022599</v>
       </c>
       <c r="O66">
-        <v>11.8147936</v>
+        <v>11.75564975</v>
       </c>
       <c r="P66">
-        <v>35.4443808</v>
+        <v>35.26694925</v>
       </c>
       <c r="Q66">
-        <v>51.8443808</v>
+        <v>51.66694924999999</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1365778311666725</v>
+        <v>0.1388935921658223</v>
       </c>
       <c r="T66">
-        <v>1.320928052898281</v>
+        <v>1.35462519710487</v>
       </c>
       <c r="U66">
         <v>0.0578</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.121307625391312</v>
+        <v>4.057902892692985</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.0767902572580378</v>
+        <v>0.0784009952960735</v>
       </c>
       <c r="C67">
-        <v>191.8634615184624</v>
+        <v>177.1670340962452</v>
       </c>
       <c r="D67">
-        <v>384.4084615184624</v>
+        <v>373.8050340962452</v>
       </c>
       <c r="E67">
-        <v>202.545</v>
+        <v>206.638</v>
       </c>
       <c r="F67">
-        <v>266.045</v>
+        <v>270.138</v>
       </c>
       <c r="G67">
         <v>73.5</v>
@@ -6781,45 +6781,45 @@
         <v>62.4</v>
       </c>
       <c r="M67">
-        <v>15.377401</v>
+        <v>16.5594594</v>
       </c>
       <c r="N67">
-        <v>47.022599</v>
+        <v>45.8405406</v>
       </c>
       <c r="O67">
-        <v>11.75564975</v>
+        <v>11.46013515</v>
       </c>
       <c r="P67">
-        <v>35.26694925</v>
+        <v>34.38040545</v>
       </c>
       <c r="Q67">
-        <v>51.66694924999999</v>
+        <v>50.78040545</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1388935921658223</v>
+        <v>0.1413455744002162</v>
       </c>
       <c r="T67">
-        <v>1.35462519710487</v>
+        <v>1.390304526264787</v>
       </c>
       <c r="U67">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V67">
         <v>0.25</v>
       </c>
       <c r="W67">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y67">
-        <v>4.057902892692985</v>
+        <v>3.76823895591664</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0784009952960735</v>
+        <v>0.07830548333410921</v>
       </c>
       <c r="C68">
-        <v>177.1670340962452</v>
+        <v>173.6864440701071</v>
       </c>
       <c r="D68">
-        <v>373.8050340962452</v>
+        <v>374.4174440701072</v>
       </c>
       <c r="E68">
-        <v>206.638</v>
+        <v>210.7310000000001</v>
       </c>
       <c r="F68">
-        <v>270.138</v>
+        <v>274.2310000000001</v>
       </c>
       <c r="G68">
         <v>73.5</v>
@@ -6863,28 +6863,28 @@
         <v>62.4</v>
       </c>
       <c r="M68">
-        <v>16.5594594</v>
+        <v>16.8103603</v>
       </c>
       <c r="N68">
-        <v>45.8405406</v>
+        <v>45.58963969999999</v>
       </c>
       <c r="O68">
-        <v>11.46013515</v>
+        <v>11.397409925</v>
       </c>
       <c r="P68">
-        <v>34.38040545</v>
+        <v>34.19222977499999</v>
       </c>
       <c r="Q68">
-        <v>50.78040545</v>
+        <v>50.59222977499999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1413455744002162</v>
+        <v>0.1439461616185128</v>
       </c>
       <c r="T68">
-        <v>1.390304526264787</v>
+        <v>1.428146239010154</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.76823895591664</v>
+        <v>3.711996583440272</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.07830548333410921</v>
+        <v>0.07820997137214492</v>
       </c>
       <c r="C69">
-        <v>173.6864440701071</v>
+        <v>170.2078639763839</v>
       </c>
       <c r="D69">
-        <v>374.4174440701072</v>
+        <v>375.0318639763839</v>
       </c>
       <c r="E69">
-        <v>210.7310000000001</v>
+        <v>214.824</v>
       </c>
       <c r="F69">
-        <v>274.2310000000001</v>
+        <v>278.324</v>
       </c>
       <c r="G69">
         <v>73.5</v>
@@ -6945,28 +6945,28 @@
         <v>62.4</v>
       </c>
       <c r="M69">
-        <v>16.8103603</v>
+        <v>17.0612612</v>
       </c>
       <c r="N69">
-        <v>45.58963969999999</v>
+        <v>45.3387388</v>
       </c>
       <c r="O69">
-        <v>11.397409925</v>
+        <v>11.3346847</v>
       </c>
       <c r="P69">
-        <v>34.19222977499999</v>
+        <v>34.0040541</v>
       </c>
       <c r="Q69">
-        <v>50.59222977499999</v>
+        <v>50.4040541</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1439461616185128</v>
+        <v>0.1467092855379529</v>
       </c>
       <c r="T69">
-        <v>1.428146239010154</v>
+        <v>1.468353058802107</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.711996583440272</v>
+        <v>3.657408398389681</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.07820997137214492</v>
+        <v>0.07811445941018061</v>
       </c>
       <c r="C70">
-        <v>170.2078639763839</v>
+        <v>166.7313037262512</v>
       </c>
       <c r="D70">
-        <v>375.0318639763839</v>
+        <v>375.6483037262512</v>
       </c>
       <c r="E70">
-        <v>214.824</v>
+        <v>218.917</v>
       </c>
       <c r="F70">
-        <v>278.324</v>
+        <v>282.417</v>
       </c>
       <c r="G70">
         <v>73.5</v>
@@ -7027,28 +7027,28 @@
         <v>62.4</v>
       </c>
       <c r="M70">
-        <v>17.0612612</v>
+        <v>17.3121621</v>
       </c>
       <c r="N70">
-        <v>45.3387388</v>
+        <v>45.0878379</v>
       </c>
       <c r="O70">
-        <v>11.3346847</v>
+        <v>11.271959475</v>
       </c>
       <c r="P70">
-        <v>34.0040541</v>
+        <v>33.81587842499999</v>
       </c>
       <c r="Q70">
-        <v>50.4040541</v>
+        <v>50.21587842499999</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1467092855379529</v>
+        <v>0.1496506755167117</v>
       </c>
       <c r="T70">
-        <v>1.468353058802107</v>
+        <v>1.511153866967734</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.657408398389681</v>
+        <v>3.604402479572439</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.07811445941018061</v>
+        <v>0.07801894744821633</v>
       </c>
       <c r="C71">
-        <v>166.7313037262512</v>
+        <v>163.2567732961558</v>
       </c>
       <c r="D71">
-        <v>375.6483037262512</v>
+        <v>376.2667732961559</v>
       </c>
       <c r="E71">
-        <v>218.917</v>
+        <v>223.01</v>
       </c>
       <c r="F71">
-        <v>282.417</v>
+        <v>286.51</v>
       </c>
       <c r="G71">
         <v>73.5</v>
@@ -7109,28 +7109,28 @@
         <v>62.4</v>
       </c>
       <c r="M71">
-        <v>17.3121621</v>
+        <v>17.563063</v>
       </c>
       <c r="N71">
-        <v>45.0878379</v>
+        <v>44.83693699999999</v>
       </c>
       <c r="O71">
-        <v>11.271959475</v>
+        <v>11.20923425</v>
       </c>
       <c r="P71">
-        <v>33.81587842499999</v>
+        <v>33.62770275</v>
       </c>
       <c r="Q71">
-        <v>50.21587842499999</v>
+        <v>50.02770275</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1496506755167117</v>
+        <v>0.1527881581607211</v>
       </c>
       <c r="T71">
-        <v>1.511153866967734</v>
+        <v>1.556808062344403</v>
       </c>
       <c r="U71">
         <v>0.0613</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.604402479572439</v>
+        <v>3.552911015578546</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07801894744821633</v>
+        <v>0.07792343548625205</v>
       </c>
       <c r="C72">
-        <v>163.2567732961558</v>
+        <v>159.7842827283544</v>
       </c>
       <c r="D72">
-        <v>376.2667732961559</v>
+        <v>376.8872827283544</v>
       </c>
       <c r="E72">
-        <v>223.01</v>
+        <v>227.1030000000001</v>
       </c>
       <c r="F72">
-        <v>286.51</v>
+        <v>290.6030000000001</v>
       </c>
       <c r="G72">
         <v>73.5</v>
@@ -7191,28 +7191,28 @@
         <v>62.4</v>
       </c>
       <c r="M72">
-        <v>17.563063</v>
+        <v>17.8139639</v>
       </c>
       <c r="N72">
-        <v>44.83693699999999</v>
+        <v>44.58603609999999</v>
       </c>
       <c r="O72">
-        <v>11.20923425</v>
+        <v>11.146509025</v>
       </c>
       <c r="P72">
-        <v>33.62770275</v>
+        <v>33.43952707499999</v>
       </c>
       <c r="Q72">
-        <v>50.02770275</v>
+        <v>49.83952707499999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1527881581607211</v>
+        <v>0.1561420189181105</v>
       </c>
       <c r="T72">
-        <v>1.556808062344403</v>
+        <v>1.605610822919463</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.552911015578546</v>
+        <v>3.50287001535913</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07792343548625204</v>
+        <v>0.07933992352428776</v>
       </c>
       <c r="C73">
-        <v>159.7842827283545</v>
+        <v>146.6937112472202</v>
       </c>
       <c r="D73">
-        <v>376.8872827283545</v>
+        <v>367.8897112472201</v>
       </c>
       <c r="E73">
-        <v>227.103</v>
+        <v>231.196</v>
       </c>
       <c r="F73">
-        <v>290.603</v>
+        <v>294.696</v>
       </c>
       <c r="G73">
         <v>73.5</v>
@@ -7273,45 +7273,45 @@
         <v>62.4</v>
       </c>
       <c r="M73">
-        <v>17.8139639</v>
+        <v>18.8900136</v>
       </c>
       <c r="N73">
-        <v>44.5860361</v>
+        <v>43.5099864</v>
       </c>
       <c r="O73">
-        <v>11.146509025</v>
+        <v>10.8774966</v>
       </c>
       <c r="P73">
-        <v>33.439527075</v>
+        <v>32.6324898</v>
       </c>
       <c r="Q73">
-        <v>49.839527075</v>
+        <v>49.0324898</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1561420189181105</v>
+        <v>0.1597354411581705</v>
       </c>
       <c r="T73">
-        <v>1.605610822919462</v>
+        <v>1.657899494964169</v>
       </c>
       <c r="U73">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V73">
         <v>0.25</v>
       </c>
       <c r="W73">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y73">
-        <v>3.502870015359131</v>
+        <v>3.303332719675755</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.07933992352428776</v>
+        <v>0.07926541156232345</v>
       </c>
       <c r="C74">
-        <v>146.6937112472202</v>
+        <v>143.0632949091084</v>
       </c>
       <c r="D74">
-        <v>367.8897112472201</v>
+        <v>368.3522949091084</v>
       </c>
       <c r="E74">
-        <v>231.196</v>
+        <v>235.289</v>
       </c>
       <c r="F74">
-        <v>294.696</v>
+        <v>298.789</v>
       </c>
       <c r="G74">
         <v>73.5</v>
@@ -7355,28 +7355,28 @@
         <v>62.4</v>
       </c>
       <c r="M74">
-        <v>18.8900136</v>
+        <v>19.1523749</v>
       </c>
       <c r="N74">
-        <v>43.5099864</v>
+        <v>43.24762509999999</v>
       </c>
       <c r="O74">
-        <v>10.8774966</v>
+        <v>10.811906275</v>
       </c>
       <c r="P74">
-        <v>32.6324898</v>
+        <v>32.435718825</v>
       </c>
       <c r="Q74">
-        <v>49.0324898</v>
+        <v>48.83571882499999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1597354411581705</v>
+        <v>0.1635950428234202</v>
       </c>
       <c r="T74">
-        <v>1.657899494964169</v>
+        <v>1.71406140197515</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.303332719675755</v>
+        <v>3.258081586529511</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.07926541156232345</v>
+        <v>0.07919089960035916</v>
       </c>
       <c r="C75">
-        <v>143.0632949091084</v>
+        <v>139.4340433388004</v>
       </c>
       <c r="D75">
-        <v>368.3522949091084</v>
+        <v>368.8160433388005</v>
       </c>
       <c r="E75">
-        <v>235.289</v>
+        <v>239.382</v>
       </c>
       <c r="F75">
-        <v>298.789</v>
+        <v>302.882</v>
       </c>
       <c r="G75">
         <v>73.5</v>
@@ -7437,28 +7437,28 @@
         <v>62.4</v>
       </c>
       <c r="M75">
-        <v>19.1523749</v>
+        <v>19.4147362</v>
       </c>
       <c r="N75">
-        <v>43.24762509999999</v>
+        <v>42.9852638</v>
       </c>
       <c r="O75">
-        <v>10.811906275</v>
+        <v>10.74631595</v>
       </c>
       <c r="P75">
-        <v>32.435718825</v>
+        <v>32.23894785</v>
       </c>
       <c r="Q75">
-        <v>48.83571882499999</v>
+        <v>48.63894785</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1635950428234202</v>
+        <v>0.1677515369244583</v>
       </c>
       <c r="T75">
-        <v>1.71406140197515</v>
+        <v>1.774543455679284</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.258081586529511</v>
+        <v>3.214053456981816</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.07919089960035916</v>
+        <v>0.07911638763839487</v>
       </c>
       <c r="C76">
-        <v>139.4340433388004</v>
+        <v>135.8059609411024</v>
       </c>
       <c r="D76">
-        <v>368.8160433388005</v>
+        <v>369.2809609411024</v>
       </c>
       <c r="E76">
-        <v>239.382</v>
+        <v>243.475</v>
       </c>
       <c r="F76">
-        <v>302.882</v>
+        <v>306.975</v>
       </c>
       <c r="G76">
         <v>73.5</v>
@@ -7519,28 +7519,28 @@
         <v>62.4</v>
       </c>
       <c r="M76">
-        <v>19.4147362</v>
+        <v>19.6770975</v>
       </c>
       <c r="N76">
-        <v>42.9852638</v>
+        <v>42.7229025</v>
       </c>
       <c r="O76">
-        <v>10.74631595</v>
+        <v>10.680725625</v>
       </c>
       <c r="P76">
-        <v>32.23894785</v>
+        <v>32.042176875</v>
       </c>
       <c r="Q76">
-        <v>48.63894785</v>
+        <v>48.44217687499999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1677515369244583</v>
+        <v>0.1722405505535795</v>
       </c>
       <c r="T76">
-        <v>1.774543455679284</v>
+        <v>1.839864073679748</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.214053456981816</v>
+        <v>3.171199410888724</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.07911638763839487</v>
+        <v>0.07904187567643059</v>
       </c>
       <c r="C77">
-        <v>135.8059609411024</v>
+        <v>132.1790521430589</v>
       </c>
       <c r="D77">
-        <v>369.2809609411024</v>
+        <v>369.7470521430589</v>
       </c>
       <c r="E77">
-        <v>243.475</v>
+        <v>247.568</v>
       </c>
       <c r="F77">
-        <v>306.975</v>
+        <v>311.068</v>
       </c>
       <c r="G77">
         <v>73.5</v>
@@ -7601,28 +7601,28 @@
         <v>62.4</v>
       </c>
       <c r="M77">
-        <v>19.6770975</v>
+        <v>19.9394588</v>
       </c>
       <c r="N77">
-        <v>42.7229025</v>
+        <v>42.46054119999999</v>
       </c>
       <c r="O77">
-        <v>10.680725625</v>
+        <v>10.6151353</v>
       </c>
       <c r="P77">
-        <v>32.042176875</v>
+        <v>31.8454059</v>
       </c>
       <c r="Q77">
-        <v>48.44217687499999</v>
+        <v>48.24540589999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1722405505535795</v>
+        <v>0.1771036486517941</v>
       </c>
       <c r="T77">
-        <v>1.839864073679748</v>
+        <v>1.910628076513585</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.171199410888724</v>
+        <v>3.129473102850715</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07904187567643059</v>
+        <v>0.0789673637144663</v>
       </c>
       <c r="C78">
-        <v>132.1790521430589</v>
+        <v>128.5533213940929</v>
       </c>
       <c r="D78">
-        <v>369.7470521430589</v>
+        <v>370.2143213940929</v>
       </c>
       <c r="E78">
-        <v>247.568</v>
+        <v>251.661</v>
       </c>
       <c r="F78">
-        <v>311.068</v>
+        <v>315.161</v>
       </c>
       <c r="G78">
         <v>73.5</v>
@@ -7683,28 +7683,28 @@
         <v>62.4</v>
       </c>
       <c r="M78">
-        <v>19.9394588</v>
+        <v>20.2018201</v>
       </c>
       <c r="N78">
-        <v>42.46054119999999</v>
+        <v>42.1981799</v>
       </c>
       <c r="O78">
-        <v>10.6151353</v>
+        <v>10.549544975</v>
       </c>
       <c r="P78">
-        <v>31.8454059</v>
+        <v>31.648634925</v>
       </c>
       <c r="Q78">
-        <v>48.24540589999999</v>
+        <v>48.048634925</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1771036486517941</v>
+        <v>0.1823896248455056</v>
       </c>
       <c r="T78">
-        <v>1.910628076513585</v>
+        <v>1.98754547089819</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.129473102850715</v>
+        <v>3.088830595021485</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0789673637144663</v>
+        <v>0.07889285175250199</v>
       </c>
       <c r="C79">
-        <v>128.5533213940929</v>
+        <v>124.9287731661481</v>
       </c>
       <c r="D79">
-        <v>370.2143213940929</v>
+        <v>370.6827731661481</v>
       </c>
       <c r="E79">
-        <v>251.661</v>
+        <v>255.754</v>
       </c>
       <c r="F79">
-        <v>315.161</v>
+        <v>319.254</v>
       </c>
       <c r="G79">
         <v>73.5</v>
@@ -7765,28 +7765,28 @@
         <v>62.4</v>
       </c>
       <c r="M79">
-        <v>20.2018201</v>
+        <v>20.4641814</v>
       </c>
       <c r="N79">
-        <v>42.1981799</v>
+        <v>41.9358186</v>
       </c>
       <c r="O79">
-        <v>10.549544975</v>
+        <v>10.48395465</v>
       </c>
       <c r="P79">
-        <v>31.648634925</v>
+        <v>31.45186395</v>
       </c>
       <c r="Q79">
-        <v>48.048634925</v>
+        <v>47.85186394999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1823896248455056</v>
+        <v>0.1881561443295545</v>
       </c>
       <c r="T79">
-        <v>1.98754547089819</v>
+        <v>2.071455355681395</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.088830595021485</v>
+        <v>3.04923020277762</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07889285175250199</v>
+        <v>0.07881833979053771</v>
       </c>
       <c r="C80">
-        <v>124.9287731661481</v>
+        <v>121.3054119538307</v>
       </c>
       <c r="D80">
-        <v>370.6827731661481</v>
+        <v>371.1524119538307</v>
       </c>
       <c r="E80">
-        <v>255.754</v>
+        <v>259.847</v>
       </c>
       <c r="F80">
-        <v>319.254</v>
+        <v>323.347</v>
       </c>
       <c r="G80">
         <v>73.5</v>
@@ -7847,28 +7847,28 @@
         <v>62.4</v>
       </c>
       <c r="M80">
-        <v>20.4641814</v>
+        <v>20.7265427</v>
       </c>
       <c r="N80">
-        <v>41.9358186</v>
+        <v>41.6734573</v>
       </c>
       <c r="O80">
-        <v>10.48395465</v>
+        <v>10.418364325</v>
       </c>
       <c r="P80">
-        <v>31.45186395</v>
+        <v>31.255092975</v>
       </c>
       <c r="Q80">
-        <v>47.85186394999999</v>
+        <v>47.655092975</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1881561443295545</v>
+        <v>0.1944718561454177</v>
       </c>
       <c r="T80">
-        <v>2.071455355681395</v>
+        <v>2.163356658063001</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.04923020277762</v>
+        <v>3.010632352109548</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07881833979053771</v>
+        <v>0.08342382782857341</v>
       </c>
       <c r="C81">
-        <v>121.3054119538307</v>
+        <v>90.2585930923384</v>
       </c>
       <c r="D81">
-        <v>371.1524119538307</v>
+        <v>344.1985930923385</v>
       </c>
       <c r="E81">
-        <v>259.847</v>
+        <v>263.9400000000001</v>
       </c>
       <c r="F81">
-        <v>323.347</v>
+        <v>327.4400000000001</v>
       </c>
       <c r="G81">
         <v>73.5</v>
@@ -7929,45 +7929,45 @@
         <v>62.4</v>
       </c>
       <c r="M81">
-        <v>20.7265427</v>
+        <v>23.542936</v>
       </c>
       <c r="N81">
-        <v>41.6734573</v>
+        <v>38.85706399999999</v>
       </c>
       <c r="O81">
-        <v>10.418364325</v>
+        <v>9.714265999999999</v>
       </c>
       <c r="P81">
-        <v>31.255092975</v>
+        <v>29.142798</v>
       </c>
       <c r="Q81">
-        <v>47.655092975</v>
+        <v>45.54279799999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1944718561454177</v>
+        <v>0.2014191391428671</v>
       </c>
       <c r="T81">
-        <v>2.163356658063001</v>
+        <v>2.264448090682768</v>
       </c>
       <c r="U81">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V81">
         <v>0.25</v>
       </c>
       <c r="W81">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y81">
-        <v>3.010632352109548</v>
+        <v>2.650476559083369</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.08342382782857341</v>
+        <v>0.08340781586660911</v>
       </c>
       <c r="C82">
-        <v>90.2585930923384</v>
+        <v>86.25252028761486</v>
       </c>
       <c r="D82">
-        <v>344.1985930923385</v>
+        <v>344.2855202876149</v>
       </c>
       <c r="E82">
-        <v>263.9400000000001</v>
+        <v>268.033</v>
       </c>
       <c r="F82">
-        <v>327.4400000000001</v>
+        <v>331.533</v>
       </c>
       <c r="G82">
         <v>73.5</v>
@@ -8011,28 +8011,28 @@
         <v>62.4</v>
       </c>
       <c r="M82">
-        <v>23.542936</v>
+        <v>23.8372227</v>
       </c>
       <c r="N82">
-        <v>38.85706399999999</v>
+        <v>38.56277729999999</v>
       </c>
       <c r="O82">
-        <v>9.714265999999999</v>
+        <v>9.640694324999998</v>
       </c>
       <c r="P82">
-        <v>29.142798</v>
+        <v>28.922082975</v>
       </c>
       <c r="Q82">
-        <v>45.54279799999999</v>
+        <v>45.32208297499999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2014191391428671</v>
+        <v>0.2090977150874165</v>
       </c>
       <c r="T82">
-        <v>2.264448090682768</v>
+        <v>2.376180726736194</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.650476559083369</v>
+        <v>2.61775462625518</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.08340781586660911</v>
+        <v>0.08339180390464482</v>
       </c>
       <c r="C83">
-        <v>86.25252028761486</v>
+        <v>82.24649140082857</v>
       </c>
       <c r="D83">
-        <v>344.2855202876149</v>
+        <v>344.3724914008286</v>
       </c>
       <c r="E83">
-        <v>268.033</v>
+        <v>272.126</v>
       </c>
       <c r="F83">
-        <v>331.533</v>
+        <v>335.626</v>
       </c>
       <c r="G83">
         <v>73.5</v>
@@ -8093,28 +8093,28 @@
         <v>62.4</v>
       </c>
       <c r="M83">
-        <v>23.8372227</v>
+        <v>24.13150940000001</v>
       </c>
       <c r="N83">
-        <v>38.56277729999999</v>
+        <v>38.26849059999999</v>
       </c>
       <c r="O83">
-        <v>9.640694324999998</v>
+        <v>9.567122649999998</v>
       </c>
       <c r="P83">
-        <v>28.922082975</v>
+        <v>28.70136794999999</v>
       </c>
       <c r="Q83">
-        <v>45.32208297499999</v>
+        <v>45.10136795</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2090977150874165</v>
+        <v>0.2176294661369158</v>
       </c>
       <c r="T83">
-        <v>2.376180726736194</v>
+        <v>2.50032810012889</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.61775462625518</v>
+        <v>2.585830789349629</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.08339180390464482</v>
+        <v>0.08337579194268055</v>
       </c>
       <c r="C84">
-        <v>82.24649140082857</v>
+        <v>78.24050646527053</v>
       </c>
       <c r="D84">
-        <v>344.3724914008286</v>
+        <v>344.4595064652706</v>
       </c>
       <c r="E84">
-        <v>272.126</v>
+        <v>276.2190000000001</v>
       </c>
       <c r="F84">
-        <v>335.626</v>
+        <v>339.7190000000001</v>
       </c>
       <c r="G84">
         <v>73.5</v>
@@ -8175,28 +8175,28 @@
         <v>62.4</v>
       </c>
       <c r="M84">
-        <v>24.13150940000001</v>
+        <v>24.42579610000001</v>
       </c>
       <c r="N84">
-        <v>38.26849059999999</v>
+        <v>37.97420389999999</v>
       </c>
       <c r="O84">
-        <v>9.567122649999998</v>
+        <v>9.493550974999998</v>
       </c>
       <c r="P84">
-        <v>28.70136794999999</v>
+        <v>28.48065292499999</v>
       </c>
       <c r="Q84">
-        <v>45.10136795</v>
+        <v>44.88065292499999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2176294661369158</v>
+        <v>0.2271649526040032</v>
       </c>
       <c r="T84">
-        <v>2.50032810012889</v>
+        <v>2.639081046861903</v>
       </c>
       <c r="U84">
         <v>0.07190000000000001</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.585830789349629</v>
+        <v>2.554676201526139</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.08337579194268055</v>
+        <v>0.08335977998071625</v>
       </c>
       <c r="C85">
-        <v>78.24050646527053</v>
+        <v>74.23456551426597</v>
       </c>
       <c r="D85">
-        <v>344.4595064652706</v>
+        <v>344.546565514266</v>
       </c>
       <c r="E85">
-        <v>276.2190000000001</v>
+        <v>280.3120000000001</v>
       </c>
       <c r="F85">
-        <v>339.7190000000001</v>
+        <v>343.8120000000001</v>
       </c>
       <c r="G85">
         <v>73.5</v>
@@ -8257,28 +8257,28 @@
         <v>62.4</v>
       </c>
       <c r="M85">
-        <v>24.42579610000001</v>
+        <v>24.72008280000001</v>
       </c>
       <c r="N85">
-        <v>37.97420389999999</v>
+        <v>37.67991719999999</v>
       </c>
       <c r="O85">
-        <v>9.493550974999998</v>
+        <v>9.419979299999998</v>
       </c>
       <c r="P85">
-        <v>28.48065292499999</v>
+        <v>28.25993789999999</v>
       </c>
       <c r="Q85">
-        <v>44.88065292499999</v>
+        <v>44.65993789999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2271649526040032</v>
+        <v>0.2378923748794766</v>
       </c>
       <c r="T85">
-        <v>2.639081046861903</v>
+        <v>2.795178111936542</v>
       </c>
       <c r="U85">
         <v>0.07190000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.554676201526139</v>
+        <v>2.524263389603209</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.08335977998071625</v>
+        <v>0.08583001801875195</v>
       </c>
       <c r="C86">
-        <v>74.23456551426602</v>
+        <v>57.21134512282015</v>
       </c>
       <c r="D86">
-        <v>344.546565514266</v>
+        <v>331.6163451228201</v>
       </c>
       <c r="E86">
-        <v>280.312</v>
+        <v>284.405</v>
       </c>
       <c r="F86">
-        <v>343.812</v>
+        <v>347.905</v>
       </c>
       <c r="G86">
         <v>73.5</v>
@@ -8339,45 +8339,45 @@
         <v>62.4</v>
       </c>
       <c r="M86">
-        <v>24.7200828</v>
+        <v>26.371199</v>
       </c>
       <c r="N86">
-        <v>37.67991719999999</v>
+        <v>36.028801</v>
       </c>
       <c r="O86">
-        <v>9.419979299999998</v>
+        <v>9.00720025</v>
       </c>
       <c r="P86">
-        <v>28.25993789999999</v>
+        <v>27.02160075</v>
       </c>
       <c r="Q86">
-        <v>44.65993789999999</v>
+        <v>43.42160075</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2378923748794765</v>
+        <v>0.250050120125013</v>
       </c>
       <c r="T86">
-        <v>2.79517811193654</v>
+        <v>2.972088119021132</v>
       </c>
       <c r="U86">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V86">
         <v>0.25</v>
       </c>
       <c r="W86">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y86">
-        <v>2.524263389603209</v>
+        <v>2.366217781755013</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.08583001801875195</v>
+        <v>0.08584325605678766</v>
       </c>
       <c r="C87">
-        <v>57.21134512282015</v>
+        <v>53.05166576381453</v>
       </c>
       <c r="D87">
-        <v>331.6163451228201</v>
+        <v>331.5496657638145</v>
       </c>
       <c r="E87">
-        <v>284.405</v>
+        <v>288.498</v>
       </c>
       <c r="F87">
-        <v>347.905</v>
+        <v>351.998</v>
       </c>
       <c r="G87">
         <v>73.5</v>
@@ -8421,28 +8421,28 @@
         <v>62.4</v>
       </c>
       <c r="M87">
-        <v>26.371199</v>
+        <v>26.6814484</v>
       </c>
       <c r="N87">
-        <v>36.028801</v>
+        <v>35.7185516</v>
       </c>
       <c r="O87">
-        <v>9.00720025</v>
+        <v>8.929637899999999</v>
       </c>
       <c r="P87">
-        <v>27.02160075</v>
+        <v>26.7889137</v>
       </c>
       <c r="Q87">
-        <v>43.42160075</v>
+        <v>43.1889137</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.250050120125013</v>
+        <v>0.2639446861199118</v>
       </c>
       <c r="T87">
-        <v>2.972088119021132</v>
+        <v>3.174270984260665</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.366217781755013</v>
+        <v>2.338703621502047</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.08584325605678766</v>
+        <v>0.08585649409482338</v>
       </c>
       <c r="C88">
-        <v>53.05166576381453</v>
+        <v>48.89201321436258</v>
       </c>
       <c r="D88">
-        <v>331.5496657638145</v>
+        <v>331.4830132143626</v>
       </c>
       <c r="E88">
-        <v>288.498</v>
+        <v>292.591</v>
       </c>
       <c r="F88">
-        <v>351.998</v>
+        <v>356.091</v>
       </c>
       <c r="G88">
         <v>73.5</v>
@@ -8503,28 +8503,28 @@
         <v>62.4</v>
       </c>
       <c r="M88">
-        <v>26.6814484</v>
+        <v>26.9916978</v>
       </c>
       <c r="N88">
-        <v>35.7185516</v>
+        <v>35.40830219999999</v>
       </c>
       <c r="O88">
-        <v>8.929637899999999</v>
+        <v>8.852075549999999</v>
       </c>
       <c r="P88">
-        <v>26.7889137</v>
+        <v>26.55622665</v>
       </c>
       <c r="Q88">
-        <v>43.1889137</v>
+        <v>42.95622664999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2639446861199118</v>
+        <v>0.2799768776524874</v>
       </c>
       <c r="T88">
-        <v>3.174270984260665</v>
+        <v>3.407558905690895</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.338703621502047</v>
+        <v>2.311821970680184</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.08585649409482338</v>
+        <v>0.08586973213285908</v>
       </c>
       <c r="C89">
-        <v>48.89201321436258</v>
+        <v>44.73238745829872</v>
       </c>
       <c r="D89">
-        <v>331.4830132143626</v>
+        <v>331.4163874582987</v>
       </c>
       <c r="E89">
-        <v>292.591</v>
+        <v>296.684</v>
       </c>
       <c r="F89">
-        <v>356.091</v>
+        <v>360.184</v>
       </c>
       <c r="G89">
         <v>73.5</v>
@@ -8585,28 +8585,28 @@
         <v>62.4</v>
       </c>
       <c r="M89">
-        <v>26.9916978</v>
+        <v>27.3019472</v>
       </c>
       <c r="N89">
-        <v>35.40830219999999</v>
+        <v>35.09805279999999</v>
       </c>
       <c r="O89">
-        <v>8.852075549999999</v>
+        <v>8.774513199999998</v>
       </c>
       <c r="P89">
-        <v>26.55622665</v>
+        <v>26.32353959999999</v>
       </c>
       <c r="Q89">
-        <v>42.95622664999999</v>
+        <v>42.7235396</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2799768776524874</v>
+        <v>0.298681101107159</v>
       </c>
       <c r="T89">
-        <v>3.407558905690895</v>
+        <v>3.679728147359497</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.311821970680184</v>
+        <v>2.285551266467909</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.08586973213285908</v>
+        <v>0.08588297017089477</v>
       </c>
       <c r="C90">
-        <v>44.73238745829872</v>
+        <v>40.57278847947026</v>
       </c>
       <c r="D90">
-        <v>331.4163874582987</v>
+        <v>331.3497884794703</v>
       </c>
       <c r="E90">
-        <v>296.684</v>
+        <v>300.777</v>
       </c>
       <c r="F90">
-        <v>360.184</v>
+        <v>364.277</v>
       </c>
       <c r="G90">
         <v>73.5</v>
@@ -8667,28 +8667,28 @@
         <v>62.4</v>
       </c>
       <c r="M90">
-        <v>27.3019472</v>
+        <v>27.6121966</v>
       </c>
       <c r="N90">
-        <v>35.09805279999999</v>
+        <v>34.78780339999999</v>
       </c>
       <c r="O90">
-        <v>8.774513199999998</v>
+        <v>8.696950849999999</v>
       </c>
       <c r="P90">
-        <v>26.32353959999999</v>
+        <v>26.09085254999999</v>
       </c>
       <c r="Q90">
-        <v>42.7235396</v>
+        <v>42.49085254999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.298681101107159</v>
+        <v>0.3207860924626799</v>
       </c>
       <c r="T90">
-        <v>3.679728147359497</v>
+        <v>4.001382705695117</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.285551266467909</v>
+        <v>2.259870915159281</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.08588297017089477</v>
+        <v>0.0858962082089305</v>
       </c>
       <c r="C91">
-        <v>40.57278847947026</v>
+        <v>36.4132162617376</v>
       </c>
       <c r="D91">
-        <v>331.3497884794703</v>
+        <v>331.2832162617376</v>
       </c>
       <c r="E91">
-        <v>300.777</v>
+        <v>304.87</v>
       </c>
       <c r="F91">
-        <v>364.277</v>
+        <v>368.37</v>
       </c>
       <c r="G91">
         <v>73.5</v>
@@ -8749,28 +8749,28 @@
         <v>62.4</v>
       </c>
       <c r="M91">
-        <v>27.6121966</v>
+        <v>27.922446</v>
       </c>
       <c r="N91">
-        <v>34.78780339999999</v>
+        <v>34.477554</v>
       </c>
       <c r="O91">
-        <v>8.696950849999999</v>
+        <v>8.619388499999999</v>
       </c>
       <c r="P91">
-        <v>26.09085254999999</v>
+        <v>25.8581655</v>
       </c>
       <c r="Q91">
-        <v>42.49085254999999</v>
+        <v>42.2581655</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3207860924626799</v>
+        <v>0.347312082089305</v>
       </c>
       <c r="T91">
-        <v>4.001382705695117</v>
+        <v>4.387368175697863</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.259870915159281</v>
+        <v>2.234761238324178</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.0858962082089305</v>
+        <v>0.0859094462469662</v>
       </c>
       <c r="C92">
-        <v>36.4132162617376</v>
+        <v>32.25367078897415</v>
       </c>
       <c r="D92">
-        <v>331.2832162617376</v>
+        <v>331.2166707889742</v>
       </c>
       <c r="E92">
-        <v>304.87</v>
+        <v>308.963</v>
       </c>
       <c r="F92">
-        <v>368.37</v>
+        <v>372.463</v>
       </c>
       <c r="G92">
         <v>73.5</v>
@@ -8831,28 +8831,28 @@
         <v>62.4</v>
       </c>
       <c r="M92">
-        <v>27.922446</v>
+        <v>28.2326954</v>
       </c>
       <c r="N92">
-        <v>34.477554</v>
+        <v>34.16730459999999</v>
       </c>
       <c r="O92">
-        <v>8.619388499999999</v>
+        <v>8.541826149999999</v>
       </c>
       <c r="P92">
-        <v>25.8581655</v>
+        <v>25.62547845</v>
       </c>
       <c r="Q92">
-        <v>42.2581655</v>
+        <v>42.02547844999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.347312082089305</v>
+        <v>0.3797327360774023</v>
       </c>
       <c r="T92">
-        <v>4.387368175697863</v>
+        <v>4.859128194590106</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.234761238324178</v>
+        <v>2.210203422518418</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.0859094462469662</v>
+        <v>0.08592268428500191</v>
       </c>
       <c r="C93">
-        <v>32.25367078897415</v>
+        <v>28.0941520450661</v>
       </c>
       <c r="D93">
-        <v>331.2166707889742</v>
+        <v>331.1501520450661</v>
       </c>
       <c r="E93">
-        <v>308.963</v>
+        <v>313.056</v>
       </c>
       <c r="F93">
-        <v>372.463</v>
+        <v>376.556</v>
       </c>
       <c r="G93">
         <v>73.5</v>
@@ -8913,28 +8913,28 @@
         <v>62.4</v>
       </c>
       <c r="M93">
-        <v>28.2326954</v>
+        <v>28.5429448</v>
       </c>
       <c r="N93">
-        <v>34.16730459999999</v>
+        <v>33.85705519999999</v>
       </c>
       <c r="O93">
-        <v>8.541826149999999</v>
+        <v>8.464263799999998</v>
       </c>
       <c r="P93">
-        <v>25.62547845</v>
+        <v>25.39279139999999</v>
       </c>
       <c r="Q93">
-        <v>42.02547844999999</v>
+        <v>41.79279139999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3797327360774023</v>
+        <v>0.4202585535625241</v>
       </c>
       <c r="T93">
-        <v>4.859128194590106</v>
+        <v>5.448828218205412</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.210203422518418</v>
+        <v>2.186179472273652</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.08592268428500191</v>
+        <v>0.08593592232303762</v>
       </c>
       <c r="C94">
-        <v>28.0941520450661</v>
+        <v>23.93466001391278</v>
       </c>
       <c r="D94">
-        <v>331.1501520450661</v>
+        <v>331.0836600139128</v>
       </c>
       <c r="E94">
-        <v>313.056</v>
+        <v>317.1490000000001</v>
       </c>
       <c r="F94">
-        <v>376.556</v>
+        <v>380.6490000000001</v>
       </c>
       <c r="G94">
         <v>73.5</v>
@@ -8995,28 +8995,28 @@
         <v>62.4</v>
       </c>
       <c r="M94">
-        <v>28.5429448</v>
+        <v>28.85319420000001</v>
       </c>
       <c r="N94">
-        <v>33.85705519999999</v>
+        <v>33.54680579999999</v>
       </c>
       <c r="O94">
-        <v>8.464263799999998</v>
+        <v>8.386701449999997</v>
       </c>
       <c r="P94">
-        <v>25.39279139999999</v>
+        <v>25.16010434999999</v>
       </c>
       <c r="Q94">
-        <v>41.79279139999999</v>
+        <v>41.56010434999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4202585535625241</v>
+        <v>0.4723631760433948</v>
       </c>
       <c r="T94">
-        <v>5.448828218205412</v>
+        <v>6.207013962853662</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.186179472273652</v>
+        <v>2.162672166120172</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.08593592232303762</v>
+        <v>0.08594916036107332</v>
       </c>
       <c r="C95">
-        <v>23.93466001391278</v>
+        <v>19.77519467942648</v>
       </c>
       <c r="D95">
-        <v>331.0836600139128</v>
+        <v>331.0171946794265</v>
       </c>
       <c r="E95">
-        <v>317.1490000000001</v>
+        <v>321.242</v>
       </c>
       <c r="F95">
-        <v>380.6490000000001</v>
+        <v>384.742</v>
       </c>
       <c r="G95">
         <v>73.5</v>
@@ -9077,28 +9077,28 @@
         <v>62.4</v>
       </c>
       <c r="M95">
-        <v>28.85319420000001</v>
+        <v>29.1634436</v>
       </c>
       <c r="N95">
-        <v>33.54680579999999</v>
+        <v>33.2365564</v>
       </c>
       <c r="O95">
-        <v>8.386701449999997</v>
+        <v>8.309139099999999</v>
       </c>
       <c r="P95">
-        <v>25.16010434999999</v>
+        <v>24.9274173</v>
       </c>
       <c r="Q95">
-        <v>41.56010434999999</v>
+        <v>41.32741729999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4723631760433948</v>
+        <v>0.5418360060178891</v>
       </c>
       <c r="T95">
-        <v>6.207013962853662</v>
+        <v>7.217928289051327</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.162672166120172</v>
+        <v>2.139665015416766</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.08594916036107332</v>
+        <v>0.08596239839910903</v>
       </c>
       <c r="C96">
-        <v>19.77519467942648</v>
+        <v>15.61575602553199</v>
       </c>
       <c r="D96">
-        <v>331.0171946794265</v>
+        <v>330.950756025532</v>
       </c>
       <c r="E96">
-        <v>321.242</v>
+        <v>325.335</v>
       </c>
       <c r="F96">
-        <v>384.742</v>
+        <v>388.835</v>
       </c>
       <c r="G96">
         <v>73.5</v>
@@ -9159,28 +9159,28 @@
         <v>62.4</v>
       </c>
       <c r="M96">
-        <v>29.1634436</v>
+        <v>29.473693</v>
       </c>
       <c r="N96">
-        <v>33.2365564</v>
+        <v>32.92630699999999</v>
       </c>
       <c r="O96">
-        <v>8.309139099999999</v>
+        <v>8.231576749999999</v>
       </c>
       <c r="P96">
-        <v>24.9274173</v>
+        <v>24.69473025</v>
       </c>
       <c r="Q96">
-        <v>41.32741729999999</v>
+        <v>41.09473025</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5418360060178891</v>
+        <v>0.6390979679821814</v>
       </c>
       <c r="T96">
-        <v>7.217928289051327</v>
+        <v>8.633208345728063</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.139665015416766</v>
+        <v>2.1171422257808</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.08596239839910903</v>
+        <v>0.08597563643714473</v>
       </c>
       <c r="C97">
-        <v>15.61575602553199</v>
+        <v>11.45634403616754</v>
       </c>
       <c r="D97">
-        <v>330.950756025532</v>
+        <v>330.8843440361676</v>
       </c>
       <c r="E97">
-        <v>325.335</v>
+        <v>329.4280000000001</v>
       </c>
       <c r="F97">
-        <v>388.835</v>
+        <v>392.9280000000001</v>
       </c>
       <c r="G97">
         <v>73.5</v>
@@ -9241,28 +9241,28 @@
         <v>62.4</v>
       </c>
       <c r="M97">
-        <v>29.473693</v>
+        <v>29.78394240000001</v>
       </c>
       <c r="N97">
-        <v>32.92630699999999</v>
+        <v>32.61605759999999</v>
       </c>
       <c r="O97">
-        <v>8.231576749999999</v>
+        <v>8.154014399999998</v>
       </c>
       <c r="P97">
-        <v>24.69473025</v>
+        <v>24.46204319999999</v>
       </c>
       <c r="Q97">
-        <v>41.09473025</v>
+        <v>40.86204319999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.6390979679821814</v>
+        <v>0.7849909109286198</v>
       </c>
       <c r="T97">
-        <v>8.633208345728063</v>
+        <v>10.75612843074316</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.1171422257808</v>
+        <v>2.095088660928917</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.08597563643714475</v>
+        <v>0.08598887447518046</v>
       </c>
       <c r="C98">
-        <v>11.45634403616754</v>
+        <v>7.296958695283877</v>
       </c>
       <c r="D98">
-        <v>330.8843440361675</v>
+        <v>330.8179586952839</v>
       </c>
       <c r="E98">
-        <v>329.428</v>
+        <v>333.521</v>
       </c>
       <c r="F98">
-        <v>392.928</v>
+        <v>397.021</v>
       </c>
       <c r="G98">
         <v>73.5</v>
@@ -9323,28 +9323,28 @@
         <v>62.4</v>
       </c>
       <c r="M98">
-        <v>29.7839424</v>
+        <v>30.0941918</v>
       </c>
       <c r="N98">
-        <v>32.6160576</v>
+        <v>32.30580819999999</v>
       </c>
       <c r="O98">
-        <v>8.154014399999999</v>
+        <v>8.076452049999999</v>
       </c>
       <c r="P98">
-        <v>24.4620432</v>
+        <v>24.22935614999999</v>
       </c>
       <c r="Q98">
-        <v>40.8620432</v>
+        <v>40.62935614999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7849909109286179</v>
+        <v>1.028145815839347</v>
       </c>
       <c r="T98">
-        <v>10.75612843074314</v>
+        <v>14.29432857243496</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.095088660928917</v>
+        <v>2.073489808754392</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.08598887447518046</v>
+        <v>0.08600211251321617</v>
       </c>
       <c r="C99">
-        <v>7.296958695283877</v>
+        <v>3.137599986844918</v>
       </c>
       <c r="D99">
-        <v>330.8179586952839</v>
+        <v>330.7515999868449</v>
       </c>
       <c r="E99">
-        <v>333.521</v>
+        <v>337.614</v>
       </c>
       <c r="F99">
-        <v>397.021</v>
+        <v>401.114</v>
       </c>
       <c r="G99">
         <v>73.5</v>
@@ -9405,28 +9405,28 @@
         <v>62.4</v>
       </c>
       <c r="M99">
-        <v>30.0941918</v>
+        <v>30.4044412</v>
       </c>
       <c r="N99">
-        <v>32.30580819999999</v>
+        <v>31.9955588</v>
       </c>
       <c r="O99">
-        <v>8.076452049999999</v>
+        <v>7.998889699999999</v>
       </c>
       <c r="P99">
-        <v>24.22935614999999</v>
+        <v>23.9966691</v>
       </c>
       <c r="Q99">
-        <v>40.62935614999999</v>
+        <v>40.3966691</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.028145815839347</v>
+        <v>1.514455625660807</v>
       </c>
       <c r="T99">
-        <v>14.29432857243496</v>
+        <v>21.3707288558186</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.073489808754392</v>
+        <v>2.052331749481388</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.08600211251321617</v>
+        <v>0.08601535055125187</v>
       </c>
       <c r="C100">
-        <v>3.137599986844918</v>
+        <v>-1.021732105172873</v>
       </c>
       <c r="D100">
-        <v>330.7515999868449</v>
+        <v>330.6852678948271</v>
       </c>
       <c r="E100">
-        <v>337.614</v>
+        <v>341.707</v>
       </c>
       <c r="F100">
-        <v>401.114</v>
+        <v>405.207</v>
       </c>
       <c r="G100">
         <v>73.5</v>
@@ -9487,28 +9487,28 @@
         <v>62.4</v>
       </c>
       <c r="M100">
-        <v>30.4044412</v>
+        <v>30.7146906</v>
       </c>
       <c r="N100">
-        <v>31.9955588</v>
+        <v>31.6853094</v>
       </c>
       <c r="O100">
-        <v>7.998889699999999</v>
+        <v>7.921327349999999</v>
       </c>
       <c r="P100">
-        <v>23.9966691</v>
+        <v>23.76398205</v>
       </c>
       <c r="Q100">
-        <v>40.3966691</v>
+        <v>40.16398205</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.514455625660807</v>
+        <v>2.973385055125184</v>
       </c>
       <c r="T100">
-        <v>21.3707288558186</v>
+        <v>42.59992970596953</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.052331749481388</v>
+        <v>2.031601125749253</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.08601535055125187</v>
-      </c>
-      <c r="C101">
-        <v>-1.021732105172873</v>
-      </c>
-      <c r="D101">
-        <v>330.6852678948271</v>
-      </c>
-      <c r="E101">
-        <v>341.707</v>
-      </c>
-      <c r="F101">
-        <v>405.207</v>
-      </c>
-      <c r="G101">
-        <v>73.5</v>
-      </c>
-      <c r="H101">
-        <v>345.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>78.8</v>
-      </c>
-      <c r="K101">
-        <v>16.4</v>
-      </c>
-      <c r="L101">
-        <v>62.4</v>
-      </c>
-      <c r="M101">
-        <v>30.7146906</v>
-      </c>
-      <c r="N101">
-        <v>31.6853094</v>
-      </c>
-      <c r="O101">
-        <v>7.921327349999999</v>
-      </c>
-      <c r="P101">
-        <v>23.76398205</v>
-      </c>
-      <c r="Q101">
-        <v>40.16398205</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.973385055125184</v>
-      </c>
-      <c r="T101">
-        <v>42.59992970596953</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.25</v>
-      </c>
-      <c r="W101">
-        <v>0.05685</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.031601125749253</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
